--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>41</v>
       </c>
       <c r="T2" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="U2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>46038</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45342</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45546</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45908</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44772</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45561</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44868</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>44826</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44559</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45747</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45579</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>45987</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45937</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45610</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44670</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45110</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45523</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>46177</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>45819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45264</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45562</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44645</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>46177</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46182</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>44925</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45019</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>45470</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45874</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45676</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>46085</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46275</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45831</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45938</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45952</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>46161</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45160</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>46104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45511</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44593</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45562</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45993</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>46272</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45965</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>46282</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45250</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45434</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44566</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45019</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44543</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>45684</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44673</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45834</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45912</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45993</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>46164</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>46055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45567</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46093</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>46196</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>46204</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45107</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44619</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>46269</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46027</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>46274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45803</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45762</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44715</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44715</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44644</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45275</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45099</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45576</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45147</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45470</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44944</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>46139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45723</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45909</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>46146</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45840</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45939</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45938</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>46150</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>46150</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>46155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45981</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45343</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>44772</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45098</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>46006</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45426</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>46052</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45481</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>46182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>46078</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45086</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>46195</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>46104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45043</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>46113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44631</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>46202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45120</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45110</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45006</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46262</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45569</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44837</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44931</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>46269</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45624</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>46272</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45749</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>46275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45488</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>46283</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45558</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>46135</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44824</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44784</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44652</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44788</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44470</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44489</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44846</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44606</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44854</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44687</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>44524</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44742</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44841</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44860</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>44467</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44813</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44846</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44859</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>44599</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44872</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44802</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>44609</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44851</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44846</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44619</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44463</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44599</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44830</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>44588</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44839</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44840</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44741</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44606</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44846</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>44714</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44606</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44838</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44606</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44475</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44631</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44533</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44581</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45418</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45037</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44503</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>44944</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45531</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45501</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45524</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45630</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45567</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45470</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45037</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45211</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45484</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45681</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45681</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45252</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45670</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45720</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44818</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45722</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45572</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45572</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44610</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45677</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45012</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45428</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45068</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44840</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45392</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45345</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>44606</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45301</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45247</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45401</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45573</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45309</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45028</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45691</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45022</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44841</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44984</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45761</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>44467</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>45604</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45749</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45775</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44931</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44734</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45222</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>45580</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45756</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44679</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44749</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45702</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45702</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45407</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45455</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45740</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45463</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44574</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45561</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>44980</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44592</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44483</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45471</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>44917</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44874</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45771</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45183</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45070</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>45604</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45722</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44740</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44825</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44606</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44847</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45646</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45635</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45041</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45371</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>44619</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45091</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>45091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>44515</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>44774</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45202</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>44908</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45055</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45470</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45446</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45356</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44620</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45481</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45646</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45348</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45462</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45103</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45189</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>44983</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44874</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44511</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45540</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45091</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44846</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44914</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45938</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45112</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45937</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45636</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>46139</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45399</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45737</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45894</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45894</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>44606</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45838</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44914</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45572</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45905</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45897</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45897</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45898</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44825</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45630</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45901</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45576</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45901</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45902</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45803</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44900</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45478</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45469</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45827</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45904</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45904</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45904</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45316</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45909</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45812</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45909</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45835</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46140</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>44629</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45912</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45912</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>44846</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>45915</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46140</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>46140</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46070</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>46141</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45915</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45912</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45488</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45912</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45965</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45917</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45917</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45552</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45916</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45919</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45918</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45525</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45432</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>46141</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44820</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45923</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44727</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45923</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>45922</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>45405</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45925</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45908</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45923</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45747</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45376</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45926</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>45926</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45929</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45926</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45930</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45317</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44987</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45930</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>46141</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>46141</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45714</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45932</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44805</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>45933</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>46146</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45252</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>44740</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36913,7 +36913,7 @@
         <v>45747</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44606</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45709</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45709</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45711</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45939</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>46146</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>45938</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>45938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45405</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>46146</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45615</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45939</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>45940</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45253</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45943</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45790</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45940</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>45944</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46148</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45944</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45944</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44742</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44839</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45946</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45950</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46153</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46153</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45951</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45951</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45952</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45953</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45953</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45952</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45952</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45952</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45953</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45953</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45173</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45952</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>46150</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45953</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45952</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45952</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45198</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45957</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45957</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45957</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45957</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45957</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45737</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45957</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45957</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45957</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45957</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45298</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45959</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45639</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45692</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45590</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45681</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45940</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44628</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45966</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>45966</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>45273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44920</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45167</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>46154</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>46154</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45972</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45975</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45965</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45975</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45975</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45975</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46155</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45980</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45981</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45505</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45985</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45982</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45982</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>45982</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45982</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44944</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45641</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45586</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45986</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46156</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45343</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45986</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>46161</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46161</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>46010</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45988</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45593</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>46161</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46048</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>46161</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46161</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45037</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>44652</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45989</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45082</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46161</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>44672</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45898</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>45692</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>46160</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45992</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45993</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45992</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45992</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45993</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45993</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>46161</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45041</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45427</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45226</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46160</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45722</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>46162</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>45741</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>46161</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45166</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>46167</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>46001</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45120</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>44839</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>46000</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>44900</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>46001</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>46000</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>44981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45720</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>44840</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>46006</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>46006</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>46006</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>46006</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>46164</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>46167</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45140</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>46006</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45771</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>46008</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>46167</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45488</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>46008</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45180</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>46013</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>46010</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>46010</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45042</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>44487</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>46014</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45706</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>46030</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>44790</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>46167</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>45345</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46169</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>44944</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>46168</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>46167</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46021</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46021</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>46020</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45037</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45569</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45761</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45301</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>46027</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45078</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45106</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>46029</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>46029</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>46029</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>46029</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45687</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>46031</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>45065</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45441</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>45561</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>46030</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45448</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>46170</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>46034</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>46171</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45581</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45512</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>44594</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>46041</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>46041</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51851,7 +51851,7 @@
         <v>46038</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45007</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>46043</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>46043</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>46174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>45030</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>46044</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>46044</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52440,7 +52440,7 @@
         <v>46044</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52513,7 +52513,7 @@
         <v>46044</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>44949</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45623</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45174</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52810,7 +52810,7 @@
         <v>45572</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>45194</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52961,7 +52961,7 @@
         <v>44873</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>46049</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53107,7 +53107,7 @@
         <v>46048</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>46049</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53253,7 +53253,7 @@
         <v>46049</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53326,7 +53326,7 @@
         <v>46050</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         <v>46050</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>46050</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>46050</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>46052</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>46008</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>46178</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>46178</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53920,7 +53920,7 @@
         <v>45016</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45470</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45252</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>45623</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>46177</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>46177</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>46178</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>46059</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>46059</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>46058</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46059</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>45832</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>45524</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44473</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>46063</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>44473</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>45670</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55191,7 +55191,7 @@
         <v>46064</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>46064</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55337,7 +55337,7 @@
         <v>45698</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>46064</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>46064</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>46066</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>46069</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45078</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46182</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45616</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>46182</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>46071</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>46071</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45041</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46182</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46073</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>46182</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45271</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>45744</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56588,7 +56588,7 @@
         <v>46073</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>45505</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45559</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56807,7 +56807,7 @@
         <v>46078</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56880,7 +56880,7 @@
         <v>46183</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56953,7 +56953,7 @@
         <v>46183</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45503</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>45385</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>46183</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45197</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>44481</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>46188</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>46187</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45208</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>46185</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>45455</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>46188</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45113</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46087</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>46185</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>46185</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45244</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45616</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58312,7 +58312,7 @@
         <v>45597</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58390,7 +58390,7 @@
         <v>46091</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>45530</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>45309</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>46091</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>45469</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45205</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>46093</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46098</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45089</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>46191</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45249</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>46191</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>46099</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59359,7 +59359,7 @@
         <v>46100</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59432,7 +59432,7 @@
         <v>46100</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45642</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59578,7 +59578,7 @@
         <v>46195</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>46195</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>46195</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>45250</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>46105</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>46198</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>46105</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>46105</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>46105</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60250,7 +60250,7 @@
         <v>46105</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>44939</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60396,7 +60396,7 @@
         <v>46107</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60474,7 +60474,7 @@
         <v>46198</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>46107</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60625,7 +60625,7 @@
         <v>46198</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45735</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
         <v>45735</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45579</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60917,7 +60917,7 @@
         <v>46244</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>46113</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61068,7 +61068,7 @@
         <v>45215</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61141,7 +61141,7 @@
         <v>45714</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>46120</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>46119</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61365,7 +61365,7 @@
         <v>46122</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61438,7 +61438,7 @@
         <v>46122</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>46126</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61584,7 +61584,7 @@
         <v>46244</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>46245</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>45426</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61803,7 +61803,7 @@
         <v>45392</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61876,7 +61876,7 @@
         <v>46245</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61949,7 +61949,7 @@
         <v>45708</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>45531</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>46244</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45199</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>46246</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>45629</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>44873</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45230</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45755</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>45883</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>45013</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>46205</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45722</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46205</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62976,7 +62976,7 @@
         <v>45120</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>44805</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63127,7 +63127,7 @@
         <v>45539</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63200,7 +63200,7 @@
         <v>46204</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45884</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46041</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45447</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45225</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>46247</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45167</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>46246</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63799,7 +63799,7 @@
         <v>46205</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>46246</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63945,7 +63945,7 @@
         <v>46247</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64018,7 +64018,7 @@
         <v>45244</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64091,7 +64091,7 @@
         <v>46251</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>45471</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64242,7 +64242,7 @@
         <v>45478</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64315,7 +64315,7 @@
         <v>46251</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>46251</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64466,7 +64466,7 @@
         <v>46251</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45706</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         <v>46205</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64690,7 +64690,7 @@
         <v>46205</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>46205</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>45009</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64919,7 +64919,7 @@
         <v>45033</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64997,7 +64997,7 @@
         <v>46251</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65070,7 +65070,7 @@
         <v>45047</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>45714</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>46206</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46205</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65372,7 +65372,7 @@
         <v>45099</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65450,7 +65450,7 @@
         <v>46248</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65523,7 +65523,7 @@
         <v>45111</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65596,7 +65596,7 @@
         <v>45594</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65669,7 +65669,7 @@
         <v>46252</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65742,7 +65742,7 @@
         <v>45706</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>46245</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65893,7 +65893,7 @@
         <v>46252</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65966,7 +65966,7 @@
         <v>46252</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66044,7 +66044,7 @@
         <v>46252</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>45440</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66190,7 +66190,7 @@
         <v>45530</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66268,7 +66268,7 @@
         <v>46209</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66346,7 +66346,7 @@
         <v>46211</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66424,7 +66424,7 @@
         <v>46212</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66502,7 +66502,7 @@
         <v>46254</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66575,7 +66575,7 @@
         <v>46255</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66648,7 +66648,7 @@
         <v>46211</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66726,7 +66726,7 @@
         <v>46212</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66804,7 +66804,7 @@
         <v>45544</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66877,7 +66877,7 @@
         <v>46252</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66950,7 +66950,7 @@
         <v>46254</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67023,7 +67023,7 @@
         <v>46254</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67096,7 +67096,7 @@
         <v>46211</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67169,7 +67169,7 @@
         <v>46212</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67247,7 +67247,7 @@
         <v>46259</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67325,7 +67325,7 @@
         <v>45040</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67403,7 +67403,7 @@
         <v>45362</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67476,7 +67476,7 @@
         <v>46259</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>46259</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67627,7 +67627,7 @@
         <v>45048</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67700,7 +67700,7 @@
         <v>46259</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67773,7 +67773,7 @@
         <v>46259</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46213</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67929,7 +67929,7 @@
         <v>46259</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68007,7 +68007,7 @@
         <v>46213</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68085,7 +68085,7 @@
         <v>46259</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         <v>46259</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68236,7 +68236,7 @@
         <v>46260</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68309,7 +68309,7 @@
         <v>46260</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68382,7 +68382,7 @@
         <v>45216</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68460,7 +68460,7 @@
         <v>45217</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68538,7 +68538,7 @@
         <v>45217</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68616,7 +68616,7 @@
         <v>45615</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68689,7 +68689,7 @@
         <v>44550</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68762,7 +68762,7 @@
         <v>45168</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68835,7 +68835,7 @@
         <v>45561</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68908,7 +68908,7 @@
         <v>46262</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68981,7 +68981,7 @@
         <v>44802</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69054,7 +69054,7 @@
         <v>46262</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69132,7 +69132,7 @@
         <v>46198</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69205,7 +69205,7 @@
         <v>46262</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69283,7 +69283,7 @@
         <v>46262</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69361,7 +69361,7 @@
         <v>46262</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69439,7 +69439,7 @@
         <v>45154</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69512,7 +69512,7 @@
         <v>45261</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69585,7 +69585,7 @@
         <v>46219</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69658,7 +69658,7 @@
         <v>46265</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69731,7 +69731,7 @@
         <v>45484</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69804,7 +69804,7 @@
         <v>45427</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69877,7 +69877,7 @@
         <v>45741</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69950,7 +69950,7 @@
         <v>44715</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70023,7 +70023,7 @@
         <v>45260</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70096,7 +70096,7 @@
         <v>45755</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70169,7 +70169,7 @@
         <v>46223</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70242,7 +70242,7 @@
         <v>45616</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70315,7 +70315,7 @@
         <v>46269</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70393,7 +70393,7 @@
         <v>45636</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70466,7 +70466,7 @@
         <v>45033</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70539,7 +70539,7 @@
         <v>46269</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70612,7 +70612,7 @@
         <v>46268</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70685,7 +70685,7 @@
         <v>44937</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70758,7 +70758,7 @@
         <v>44480</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70831,7 +70831,7 @@
         <v>46269</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70904,7 +70904,7 @@
         <v>46268</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70977,7 +70977,7 @@
         <v>45530</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71050,7 +71050,7 @@
         <v>45777</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71123,7 +71123,7 @@
         <v>46269</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71201,7 +71201,7 @@
         <v>46230</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71279,7 +71279,7 @@
         <v>45747</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71352,7 +71352,7 @@
         <v>46195</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71425,7 +71425,7 @@
         <v>45636</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71498,7 +71498,7 @@
         <v>45783</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71576,7 +71576,7 @@
         <v>45783</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71654,7 +71654,7 @@
         <v>45783</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71727,7 +71727,7 @@
         <v>46268</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71805,7 +71805,7 @@
         <v>46272</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71878,7 +71878,7 @@
         <v>46272</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71951,7 +71951,7 @@
         <v>46272</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72024,7 +72024,7 @@
         <v>46273</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72097,7 +72097,7 @@
         <v>46274</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72175,7 +72175,7 @@
         <v>45785</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72248,7 +72248,7 @@
         <v>46274</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72326,7 +72326,7 @@
         <v>46233</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72404,7 +72404,7 @@
         <v>46276</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72482,7 +72482,7 @@
         <v>45785</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72555,7 +72555,7 @@
         <v>46276</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72633,7 +72633,7 @@
         <v>46276</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72706,7 +72706,7 @@
         <v>45635</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72779,7 +72779,7 @@
         <v>46276</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72852,7 +72852,7 @@
         <v>45748</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72925,7 +72925,7 @@
         <v>46279</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72998,7 +72998,7 @@
         <v>46280</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73076,7 +73076,7 @@
         <v>45484</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73149,7 +73149,7 @@
         <v>46281</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73222,7 +73222,7 @@
         <v>46280</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73295,7 +73295,7 @@
         <v>46280</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73368,7 +73368,7 @@
         <v>46280</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73441,7 +73441,7 @@
         <v>45789</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73514,7 +73514,7 @@
         <v>45792</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73587,7 +73587,7 @@
         <v>45792</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73660,7 +73660,7 @@
         <v>45792</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73733,7 +73733,7 @@
         <v>46239</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73806,7 +73806,7 @@
         <v>46240</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73884,7 +73884,7 @@
         <v>46239</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73957,7 +73957,7 @@
         <v>46240</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74030,7 +74030,7 @@
         <v>46282</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74108,7 +74108,7 @@
         <v>45516</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74181,7 +74181,7 @@
         <v>46239</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74254,7 +74254,7 @@
         <v>45632</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74327,7 +74327,7 @@
         <v>46241</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74405,7 +74405,7 @@
         <v>45243</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74478,7 +74478,7 @@
         <v>45447</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74556,7 +74556,7 @@
         <v>45811</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74634,7 +74634,7 @@
         <v>45666</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74707,7 +74707,7 @@
         <v>45237</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74780,7 +74780,7 @@
         <v>45623</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74853,7 +74853,7 @@
         <v>45769</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74926,7 +74926,7 @@
         <v>45439</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -74999,7 +74999,7 @@
         <v>45785</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75072,7 +75072,7 @@
         <v>45824</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75145,7 +75145,7 @@
         <v>45825</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75223,7 +75223,7 @@
         <v>45825</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>45825</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75379,7 +75379,7 @@
         <v>45824</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75452,7 +75452,7 @@
         <v>45824</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75525,7 +75525,7 @@
         <v>45833</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75598,7 +75598,7 @@
         <v>45832</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75671,7 +75671,7 @@
         <v>45838</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>45840</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -75817,7 +75817,7 @@
         <v>45826</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -75890,7 +75890,7 @@
         <v>45842</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -75963,7 +75963,7 @@
         <v>45846</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76036,7 +76036,7 @@
         <v>45531</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76109,7 +76109,7 @@
         <v>45803</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76182,7 +76182,7 @@
         <v>45866</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76260,7 +76260,7 @@
         <v>45868</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76338,7 +76338,7 @@
         <v>45873</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76416,7 +76416,7 @@
         <v>45873</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76494,7 +76494,7 @@
         <v>45875</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76572,7 +76572,7 @@
         <v>45875</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76650,7 +76650,7 @@
         <v>45874</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76723,7 +76723,7 @@
         <v>45876</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -76796,7 +76796,7 @@
         <v>45876</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -76869,7 +76869,7 @@
         <v>45877</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -76942,7 +76942,7 @@
         <v>45881</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77015,7 +77015,7 @@
         <v>44726</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77088,7 +77088,7 @@
         <v>44473</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77166,7 +77166,7 @@
         <v>44482</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77244,7 +77244,7 @@
         <v>45713</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77317,7 +77317,7 @@
         <v>45713</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -77390,7 +77390,7 @@
         <v>46108</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -77463,7 +77463,7 @@
         <v>46148</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>46038</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45546</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45342</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45908</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45579</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>44772</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45561</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>44826</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44868</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44559</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45987</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45610</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44670</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45110</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45523</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45264</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44925</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44645</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45562</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>46085</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45019</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45470</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45874</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45676</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45562</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>45938</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45952</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>45831</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>46161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>45873</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>45160</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>46272</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45993</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>46282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44593</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45734</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45250</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45434</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44566</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44619</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45834</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45912</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45567</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>46093</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45579</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46164</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44673</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46204</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>46027</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46269</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>46274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45019</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45762</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44715</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44715</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45251</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>46052</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45909</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>46078</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44644</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44631</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45938</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>46113</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45569</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45579</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>46006</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45470</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44837</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45723</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45343</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>46155</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46182</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45481</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>46195</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>46202</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45043</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45120</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>46262</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44904</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44772</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46269</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45275</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46283</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45576</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46287</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45147</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44931</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45426</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45624</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>46135</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44587</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44788</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44652</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44777</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44470</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44489</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44846</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44606</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>44687</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44854</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44860</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44467</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44846</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>44859</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44599</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44802</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44609</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44851</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44619</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44599</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44830</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44588</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44839</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44741</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>44606</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44846</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44714</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44606</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44606</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>44475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44631</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44533</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44581</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45405</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44846</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44825</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45771</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45202</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44790</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44841</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45714</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45440</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45418</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45448</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44481</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45427</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44846</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44840</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45252</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45301</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44480</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45463</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45037</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45593</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45503</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44467</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>46014</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>46020</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45345</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>46021</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>46021</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45516</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45455</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45140</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45573</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>46027</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>46029</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45632</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45471</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45253</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45446</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>44873</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45243</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44606</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45484</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>46029</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>46029</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>46029</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45478</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>44874</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>46030</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45481</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44874</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45531</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45636</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45428</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45470</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45471</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45033</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>46038</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45838</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45894</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46041</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45545</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>46041</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46044</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>46044</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46044</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45897</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46043</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45898</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>46044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45484</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46043</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45901</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45901</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>46048</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45803</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>46050</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45904</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46050</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45904</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45904</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45904</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46049</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46050</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>46050</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46049</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45539</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44939</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46052</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45909</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45405</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45912</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45912</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>44944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46058</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45912</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45524</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45912</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>46059</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>46059</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45488</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44473</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45916</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44473</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46059</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45915</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45561</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45524</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45918</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45009</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45917</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45019</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45552</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46064</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46064</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45919</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>46066</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46069</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45581</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45923</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>46071</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>45925</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45926</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45505</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45567</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>46071</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46073</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>45926</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45636</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46073</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45559</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46078</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45047</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45930</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45929</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>44629</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44606</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45932</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45666</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45722</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45447</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46087</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45933</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>44937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>46091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46091</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45938</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45702</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45938</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45938</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>44983</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45756</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45940</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45940</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45939</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>45399</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45944</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45944</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45943</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45944</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45211</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46098</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45946</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>46100</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46100</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46099</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46105</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>46105</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>46105</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45952</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>46105</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>46105</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45951</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45951</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46107</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45952</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45952</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45952</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46107</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45594</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45952</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45952</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45953</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45811</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45953</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45953</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45271</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45629</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45953</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45953</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45623</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45957</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45957</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45957</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45957</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45957</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>46113</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45348</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45957</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45958</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45013</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45957</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45959</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45244</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>46120</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45580</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46122</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45007</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45940</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46122</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45623</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45641</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45966</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45966</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44487</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45041</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>45041</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45972</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45769</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45706</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45639</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46126</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45439</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45975</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44805</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45975</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45041</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45975</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45975</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45982</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45981</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45982</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>45427</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45986</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45986</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45883</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>44900</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>44774</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45586</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45988</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45938</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45989</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>44740</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45992</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45992</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45722</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45993</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45174</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45993</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45722</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45993</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45884</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45737</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46000</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45937</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46000</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46000</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>44818</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>46001</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>44917</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>46001</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45905</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45120</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45447</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45530</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46006</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46006</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>46006</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>45544</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>46006</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46006</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45646</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46140</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46008</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45572</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45785</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46008</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>46010</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>46010</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45316</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>46013</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45747</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45824</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>46041</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45824</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45827</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45824</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45835</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45744</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45908</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>44488</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45037</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45037</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45505</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45576</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45698</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45670</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>46070</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45022</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45825</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>46140</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45923</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>44840</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45825</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>46141</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45825</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45432</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45965</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>46141</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45812</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45720</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>44483</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46141</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>46141</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45923</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45111</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45775</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45714</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45761</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46141</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45065</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>46146</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45572</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45747</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45210</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>46146</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45790</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46146</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>44914</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>46148</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45755</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45469</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>46150</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45832</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45833</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45082</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44908</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46153</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>46154</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>46154</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45055</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>46155</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45838</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>44920</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45298</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>45965</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
         <v>46156</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>44825</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45376</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45525</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>46160</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>44873</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45343</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49792,7 +49792,7 @@
         <v>45103</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45089</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>46160</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45898</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>46161</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>46161</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45840</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45826</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>46162</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46161</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46161</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>46161</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46048</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46161</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45842</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45112</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>46010</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45846</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>46164</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>46168</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>46167</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>46167</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>44847</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45385</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51642,7 +51642,7 @@
         <v>46030</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>46167</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45371</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>46167</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>46167</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>45120</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52085,7 +52085,7 @@
         <v>45113</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>45488</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45392</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>46169</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>46170</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44931</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45531</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45455</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45803</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>44515</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>46171</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45866</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>44914</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45868</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46174</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45698</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         <v>46008</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45832</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45016</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>45531</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>46177</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45579</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>46177</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>46178</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         <v>46178</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53960,7 +53960,7 @@
         <v>45616</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45012</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45771</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>46178</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54257,7 +54257,7 @@
         <v>45692</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54330,7 +54330,7 @@
         <v>44984</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45755</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45037</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>45426</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46182</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>46183</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45873</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>46182</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>46182</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45623</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>46183</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>46183</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46182</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45142</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45478</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>46185</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46187</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>46185</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>46185</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45572</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45040</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44511</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45616</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45104</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45590</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>45670</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>46188</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>46188</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>45873</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>46191</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>45250</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45761</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45876</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45875</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>46195</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57028,7 +57028,7 @@
         <v>45875</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>46195</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45876</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>44594</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57325,7 +57325,7 @@
         <v>46195</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57403,7 +57403,7 @@
         <v>44628</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57476,7 +57476,7 @@
         <v>45642</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>45028</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>45199</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45877</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45068</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45309</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57997,7 +57997,7 @@
         <v>44550</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58070,7 +58070,7 @@
         <v>45048</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
         <v>46198</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>46198</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58289,7 +58289,7 @@
         <v>45881</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>46205</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58440,7 +58440,7 @@
         <v>46205</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>46205</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>46205</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>46205</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45646</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>46205</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45356</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46205</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59112,7 +59112,7 @@
         <v>45677</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>45569</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>46252</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>45512</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59409,7 +59409,7 @@
         <v>46251</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>46209</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59560,7 +59560,7 @@
         <v>45091</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59633,7 +59633,7 @@
         <v>46252</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>46206</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59779,7 +59779,7 @@
         <v>45735</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45735</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         <v>46251</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         <v>45194</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60076,7 +60076,7 @@
         <v>46251</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60149,7 +60149,7 @@
         <v>46251</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45691</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>46251</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>46252</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>46252</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>45407</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>46211</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>46211</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>46211</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>45166</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45708</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45709</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>45709</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45711</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45392</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>46213</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>46254</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>45099</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>44606</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46254</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>46254</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46212</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>45197</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61873,7 +61873,7 @@
         <v>46213</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61951,7 +61951,7 @@
         <v>45687</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>45441</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>46212</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>46252</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62253,7 +62253,7 @@
         <v>45681</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62326,7 +62326,7 @@
         <v>45681</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>46255</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>44619</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>45167</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>46212</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62701,7 +62701,7 @@
         <v>46259</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>46259</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>46260</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>46259</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62998,7 +62998,7 @@
         <v>44839</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63071,7 +63071,7 @@
         <v>46259</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63149,7 +63149,7 @@
         <v>46259</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>46259</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63300,7 +63300,7 @@
         <v>46259</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63378,7 +63378,7 @@
         <v>45230</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63451,7 +63451,7 @@
         <v>46260</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63524,7 +63524,7 @@
         <v>45706</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63597,7 +63597,7 @@
         <v>45741</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>45198</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>44672</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46259</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>45252</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45180</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>45168</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46262</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>46262</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64269,7 +64269,7 @@
         <v>46262</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64347,7 +64347,7 @@
         <v>46262</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64425,7 +64425,7 @@
         <v>46262</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>44749</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64571,7 +64571,7 @@
         <v>45225</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>45469</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64717,7 +64717,7 @@
         <v>45462</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45720</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45215</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64936,7 +64936,7 @@
         <v>46265</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65009,7 +65009,7 @@
         <v>45189</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65087,7 +65087,7 @@
         <v>46223</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65160,7 +65160,7 @@
         <v>46198</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65233,7 +65233,7 @@
         <v>46268</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65306,7 +65306,7 @@
         <v>45217</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>45217</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>46268</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>44805</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65613,7 +65613,7 @@
         <v>44742</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>46269</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65764,7 +65764,7 @@
         <v>44503</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>46272</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65910,7 +65910,7 @@
         <v>46268</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65988,7 +65988,7 @@
         <v>46195</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66061,7 +66061,7 @@
         <v>46272</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66134,7 +66134,7 @@
         <v>46272</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66207,7 +66207,7 @@
         <v>46269</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66280,7 +66280,7 @@
         <v>46269</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>46269</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66431,7 +66431,7 @@
         <v>46273</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66504,7 +66504,7 @@
         <v>45317</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         <v>46274</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66655,7 +66655,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>46230</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66811,7 +66811,7 @@
         <v>45740</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66884,7 +66884,7 @@
         <v>46276</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66962,7 +66962,7 @@
         <v>46276</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67035,7 +67035,7 @@
         <v>44820</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67108,7 +67108,7 @@
         <v>45345</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67181,7 +67181,7 @@
         <v>46276</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67254,7 +67254,7 @@
         <v>46233</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>46276</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67410,7 +67410,7 @@
         <v>46280</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>46280</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67561,7 +67561,7 @@
         <v>45173</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67634,7 +67634,7 @@
         <v>45167</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67707,7 +67707,7 @@
         <v>45216</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67785,7 +67785,7 @@
         <v>46279</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67858,7 +67858,7 @@
         <v>46280</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67931,7 +67931,7 @@
         <v>45741</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68004,7 +68004,7 @@
         <v>45205</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68077,7 +68077,7 @@
         <v>46280</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>46239</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68223,7 +68223,7 @@
         <v>46239</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>46239</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68369,7 +68369,7 @@
         <v>46281</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68442,7 +68442,7 @@
         <v>45470</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68515,7 +68515,7 @@
         <v>46282</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68593,7 +68593,7 @@
         <v>44900</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68666,7 +68666,7 @@
         <v>46241</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68744,7 +68744,7 @@
         <v>46240</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68817,7 +68817,7 @@
         <v>46240</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68895,7 +68895,7 @@
         <v>46286</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68968,7 +68968,7 @@
         <v>45572</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69041,7 +69041,7 @@
         <v>45362</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69114,7 +69114,7 @@
         <v>46287</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69187,7 +69187,7 @@
         <v>44606</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69260,7 +69260,7 @@
         <v>46287</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69333,7 +69333,7 @@
         <v>46245</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69406,7 +69406,7 @@
         <v>46287</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>45226</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>44949</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45561</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>44610</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69776,7 +69776,7 @@
         <v>46287</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46287</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69932,7 +69932,7 @@
         <v>46287</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70010,7 +70010,7 @@
         <v>46244</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70083,7 +70083,7 @@
         <v>46244</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70156,7 +70156,7 @@
         <v>46244</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70229,7 +70229,7 @@
         <v>46245</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70302,7 +70302,7 @@
         <v>46245</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70380,7 +70380,7 @@
         <v>46286</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70453,7 +70453,7 @@
         <v>46287</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70526,7 +70526,7 @@
         <v>46246</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70599,7 +70599,7 @@
         <v>44679</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70672,7 +70672,7 @@
         <v>46246</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>46289</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>46290</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>45260</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>46247</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>45561</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>46246</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71188,7 +71188,7 @@
         <v>44740</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71261,7 +71261,7 @@
         <v>46247</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71334,7 +71334,7 @@
         <v>44620</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71407,7 +71407,7 @@
         <v>46248</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71480,7 +71480,7 @@
         <v>44839</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71553,7 +71553,7 @@
         <v>46289</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71626,7 +71626,7 @@
         <v>44727</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71699,7 +71699,7 @@
         <v>44981</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71772,7 +71772,7 @@
         <v>44944</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71845,7 +71845,7 @@
         <v>44944</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71918,7 +71918,7 @@
         <v>44652</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71991,7 +71991,7 @@
         <v>44944</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72064,7 +72064,7 @@
         <v>45154</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72137,7 +72137,7 @@
         <v>45309</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72215,7 +72215,7 @@
         <v>44980</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72293,7 +72293,7 @@
         <v>45042</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72366,7 +72366,7 @@
         <v>45208</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72439,7 +72439,7 @@
         <v>45597</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72517,7 +72517,7 @@
         <v>45247</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72590,7 +72590,7 @@
         <v>45030</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72663,7 +72663,7 @@
         <v>45078</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72736,7 +72736,7 @@
         <v>45635</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72814,7 +72814,7 @@
         <v>45401</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45692</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>45033</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73043,7 +73043,7 @@
         <v>45078</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73116,7 +73116,7 @@
         <v>45249</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73189,7 +73189,7 @@
         <v>45714</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73262,7 +73262,7 @@
         <v>45252</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73335,7 +73335,7 @@
         <v>45630</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73408,7 +73408,7 @@
         <v>44606</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73481,7 +73481,7 @@
         <v>44987</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73554,7 +73554,7 @@
         <v>45070</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73627,7 +73627,7 @@
         <v>45615</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73700,7 +73700,7 @@
         <v>45261</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73773,7 +73773,7 @@
         <v>45183</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73846,7 +73846,7 @@
         <v>44734</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73919,7 +73919,7 @@
         <v>45702</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73992,7 +73992,7 @@
         <v>45470</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74065,7 +74065,7 @@
         <v>44592</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74138,7 +74138,7 @@
         <v>45043</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74211,7 +74211,7 @@
         <v>45604</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74284,7 +74284,7 @@
         <v>44802</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74357,7 +74357,7 @@
         <v>45222</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74430,7 +74430,7 @@
         <v>45301</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74503,7 +74503,7 @@
         <v>45273</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74576,7 +74576,7 @@
         <v>45756</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74649,7 +74649,7 @@
         <v>45681</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74722,7 +74722,7 @@
         <v>45706</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74795,7 +74795,7 @@
         <v>45737</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74868,7 +74868,7 @@
         <v>45501</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -74941,7 +74941,7 @@
         <v>45616</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75014,7 +75014,7 @@
         <v>45722</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75087,7 +75087,7 @@
         <v>45749</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75160,7 +75160,7 @@
         <v>45604</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75233,7 +75233,7 @@
         <v>45630</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75306,7 +75306,7 @@
         <v>45530</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75384,7 +75384,7 @@
         <v>45530</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75457,7 +75457,7 @@
         <v>45260</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75530,7 +75530,7 @@
         <v>45540</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75603,7 +75603,7 @@
         <v>45747</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75676,7 +75676,7 @@
         <v>45636</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -75749,7 +75749,7 @@
         <v>45777</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45783</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -75900,7 +75900,7 @@
         <v>45783</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -75973,7 +75973,7 @@
         <v>45783</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>45785</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>45484</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76197,7 +76197,7 @@
         <v>45785</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76270,7 +76270,7 @@
         <v>45635</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76343,7 +76343,7 @@
         <v>45748</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76416,7 +76416,7 @@
         <v>45792</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76489,7 +76489,7 @@
         <v>45789</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76562,7 +76562,7 @@
         <v>45792</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76635,7 +76635,7 @@
         <v>45792</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -76708,7 +76708,7 @@
         <v>44726</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -76781,7 +76781,7 @@
         <v>44473</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -76859,7 +76859,7 @@
         <v>44482</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -76937,7 +76937,7 @@
         <v>45713</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77010,7 +77010,7 @@
         <v>45713</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77083,7 +77083,7 @@
         <v>46108</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77156,7 +77156,7 @@
         <v>46148</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77229,7 +77229,7 @@
         <v>46286</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>46038</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45546</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45342</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45908</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45579</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>44772</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45561</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>44826</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44868</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44559</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45987</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45610</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44670</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45110</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45523</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45264</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44925</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44645</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45562</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>46085</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45019</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45470</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45874</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45676</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45562</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>45938</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45952</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>45831</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>46161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>45873</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>45160</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>46272</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45993</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>46282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44593</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45734</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45250</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45434</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44566</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44619</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45834</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45912</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45567</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>46093</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45579</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46164</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44673</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46204</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>46027</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46269</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>46274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45019</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45762</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44715</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44715</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45251</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>46052</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45909</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>46078</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44644</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44631</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45938</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>46113</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45569</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45579</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>46006</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45470</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44837</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45723</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45343</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>46155</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46182</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45481</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>46195</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>46202</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45043</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45120</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>46262</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44904</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44772</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46269</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45275</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46283</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45576</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46287</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45147</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44931</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45426</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45624</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>46135</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44587</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44788</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44652</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44777</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44470</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44489</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44846</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44606</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>44687</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44854</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44860</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44467</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44846</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>44859</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44599</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44802</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44609</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44851</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44619</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44599</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44830</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44588</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44839</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44741</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>44606</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44846</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44714</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44606</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44606</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>44475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44631</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44533</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44581</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45405</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44846</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44825</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45771</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45202</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44790</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44841</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45714</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45440</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45418</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45448</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44481</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45427</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44846</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44840</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45252</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45301</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44480</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45463</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45037</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45593</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45503</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44467</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>46014</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>46020</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45345</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>46021</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>46021</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45516</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45455</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45140</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45573</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>46027</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>46029</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45632</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45471</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45253</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45446</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>44873</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45243</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44606</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45484</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>46029</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>46029</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>46029</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45478</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>44874</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>46030</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45481</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44874</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45531</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45636</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45428</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45470</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45471</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45033</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>46038</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45838</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45894</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46041</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45545</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>46041</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46044</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>46044</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46044</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45897</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46043</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45898</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>46044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45484</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46043</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45901</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45901</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>46048</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45803</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>46050</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45904</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46050</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45904</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45904</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45904</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46049</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46050</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>46050</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46049</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45539</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44939</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46052</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45909</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45405</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45912</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45912</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>44944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46058</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45912</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45524</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45912</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>46059</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>46059</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45488</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44473</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45916</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44473</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46059</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45915</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45561</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45524</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45918</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45009</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45917</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45019</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45552</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46064</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46064</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45919</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>46066</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46069</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45581</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45923</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>46071</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>45925</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45926</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45505</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45567</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>46071</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46073</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>45926</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45636</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46073</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45559</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46078</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45047</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45930</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45929</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>44629</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44606</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45932</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45666</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45722</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45447</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46087</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45933</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>44937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>46091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46091</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45938</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45702</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45938</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45938</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>44983</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45756</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45940</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45940</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45939</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>45399</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45944</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45944</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45943</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45944</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45211</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46098</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45946</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>46100</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46100</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46099</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46105</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>46105</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>46105</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45952</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>46105</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>46105</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45951</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45951</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46107</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45952</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45952</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45952</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46107</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45594</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45952</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45952</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45953</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45811</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45953</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45953</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45271</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45629</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45953</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45953</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45623</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45957</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45957</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45957</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45957</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45957</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>46113</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45348</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45957</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45958</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45013</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45957</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45959</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45244</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>46120</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45580</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46122</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45007</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45940</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46122</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45623</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45641</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45966</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45966</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44487</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45041</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>45041</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45972</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45769</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45706</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45639</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46126</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45439</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45975</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44805</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45975</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45041</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45975</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45975</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45982</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45981</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45982</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>45427</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45986</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45986</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45883</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>44900</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>44774</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45586</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45988</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45938</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45989</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>44740</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45992</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45992</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45722</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45993</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45174</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45993</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45722</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45993</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45884</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45737</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46000</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45937</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46000</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46000</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>44818</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>46001</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>44917</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>46001</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45905</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45120</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45447</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45530</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46006</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46006</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>46006</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>45544</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>46006</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46006</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45646</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46140</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46008</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45572</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45785</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46008</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>46010</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>46010</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45316</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>46013</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45747</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45824</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>46041</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45824</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45827</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45824</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45835</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45744</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45908</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>44488</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45037</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45037</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45505</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45576</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45698</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45670</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>46070</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45022</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45825</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>46140</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45923</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>44840</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45825</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>46141</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45825</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45432</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45965</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>46141</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45812</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45720</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>44483</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46141</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>46141</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45923</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45111</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45775</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45714</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45761</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46141</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45065</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>46146</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45572</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45747</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45210</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>46146</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45790</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46146</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>44914</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>46148</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45755</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45469</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>46150</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45832</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45833</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45082</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44908</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46153</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>46154</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>46154</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45055</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>46155</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45838</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>44920</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45298</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>45965</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
         <v>46156</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>44825</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45376</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45525</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49568,7 +49568,7 @@
         <v>46160</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>44873</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45343</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49792,7 +49792,7 @@
         <v>45103</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45089</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>46160</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45898</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>46161</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>46161</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45840</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45826</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>46162</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46161</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46161</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>46161</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46048</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46161</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45842</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45112</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>46010</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45846</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>46164</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>46168</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>46167</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>46167</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>44847</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45385</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51642,7 +51642,7 @@
         <v>46030</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>46167</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45371</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>46167</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>46167</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>45120</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52085,7 +52085,7 @@
         <v>45113</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>45488</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45392</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>46169</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>46170</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44931</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45531</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45455</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45803</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>44515</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>46171</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45866</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>44914</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45868</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46174</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45698</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         <v>46008</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45832</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45016</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>45531</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>46177</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45579</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>46177</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>46178</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         <v>46178</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53960,7 +53960,7 @@
         <v>45616</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45012</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45771</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>46178</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54257,7 +54257,7 @@
         <v>45692</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54330,7 +54330,7 @@
         <v>44984</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45755</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45037</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>45426</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46182</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>46183</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45873</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>46182</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>46182</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45623</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>46183</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>46183</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46182</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45142</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45478</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>46185</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46187</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>46185</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>46185</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45572</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45040</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44511</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45616</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45104</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45590</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>45670</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>46188</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>46188</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>45873</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>46191</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>45250</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45761</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45876</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45875</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>46195</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57028,7 +57028,7 @@
         <v>45875</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>46195</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45876</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>44594</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57325,7 +57325,7 @@
         <v>46195</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57403,7 +57403,7 @@
         <v>44628</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57476,7 +57476,7 @@
         <v>45642</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>45028</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>45199</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45877</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45068</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45309</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57997,7 +57997,7 @@
         <v>44550</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58070,7 +58070,7 @@
         <v>45048</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
         <v>46198</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>46198</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58289,7 +58289,7 @@
         <v>45881</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>46205</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58440,7 +58440,7 @@
         <v>46205</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>46205</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>46205</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>46205</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45646</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>46205</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45356</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46205</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59112,7 +59112,7 @@
         <v>45677</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>45569</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>46252</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>45512</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59409,7 +59409,7 @@
         <v>46251</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>46209</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59560,7 +59560,7 @@
         <v>45091</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59633,7 +59633,7 @@
         <v>46252</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>46206</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59779,7 +59779,7 @@
         <v>45735</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45735</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         <v>46251</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         <v>45194</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60076,7 +60076,7 @@
         <v>46251</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60149,7 +60149,7 @@
         <v>46251</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45691</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>46251</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>46252</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>46252</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>45407</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>46211</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>46211</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>46211</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>45166</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45708</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45709</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>45709</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45711</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45392</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>46213</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>46254</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>45099</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>44606</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46254</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>46254</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46212</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>45197</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61873,7 +61873,7 @@
         <v>46213</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61951,7 +61951,7 @@
         <v>45687</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>45441</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>46212</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>46252</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62253,7 +62253,7 @@
         <v>45681</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62326,7 +62326,7 @@
         <v>45681</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>46255</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>44619</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>45167</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>46212</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62701,7 +62701,7 @@
         <v>46259</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>46259</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>46260</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>46259</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62998,7 +62998,7 @@
         <v>44839</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63071,7 +63071,7 @@
         <v>46259</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63149,7 +63149,7 @@
         <v>46259</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>46259</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63300,7 +63300,7 @@
         <v>46259</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63378,7 +63378,7 @@
         <v>45230</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63451,7 +63451,7 @@
         <v>46260</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63524,7 +63524,7 @@
         <v>45706</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63597,7 +63597,7 @@
         <v>45741</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>45198</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>44672</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46259</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>45252</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45180</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>45168</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46262</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>46262</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64269,7 +64269,7 @@
         <v>46262</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64347,7 +64347,7 @@
         <v>46262</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64425,7 +64425,7 @@
         <v>46262</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>44749</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64571,7 +64571,7 @@
         <v>45225</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>45469</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64717,7 +64717,7 @@
         <v>45462</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45720</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45215</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64936,7 +64936,7 @@
         <v>46265</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65009,7 +65009,7 @@
         <v>45189</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65087,7 +65087,7 @@
         <v>46223</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65160,7 +65160,7 @@
         <v>46198</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65233,7 +65233,7 @@
         <v>46268</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65306,7 +65306,7 @@
         <v>45217</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>45217</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>46268</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>44805</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65613,7 +65613,7 @@
         <v>44742</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>46269</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65764,7 +65764,7 @@
         <v>44503</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>46272</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65910,7 +65910,7 @@
         <v>46268</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65988,7 +65988,7 @@
         <v>46195</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66061,7 +66061,7 @@
         <v>46272</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66134,7 +66134,7 @@
         <v>46272</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66207,7 +66207,7 @@
         <v>46269</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66280,7 +66280,7 @@
         <v>46269</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>46269</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66431,7 +66431,7 @@
         <v>46273</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66504,7 +66504,7 @@
         <v>45317</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         <v>46274</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66655,7 +66655,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>46230</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66811,7 +66811,7 @@
         <v>45740</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66884,7 +66884,7 @@
         <v>46276</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66962,7 +66962,7 @@
         <v>46276</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67035,7 +67035,7 @@
         <v>44820</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67108,7 +67108,7 @@
         <v>45345</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67181,7 +67181,7 @@
         <v>46276</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67254,7 +67254,7 @@
         <v>46233</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>46276</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67410,7 +67410,7 @@
         <v>46280</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>46280</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67561,7 +67561,7 @@
         <v>45173</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67634,7 +67634,7 @@
         <v>45167</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67707,7 +67707,7 @@
         <v>45216</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67785,7 +67785,7 @@
         <v>46279</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67858,7 +67858,7 @@
         <v>46280</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67931,7 +67931,7 @@
         <v>45741</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68004,7 +68004,7 @@
         <v>45205</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68077,7 +68077,7 @@
         <v>46280</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>46239</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68223,7 +68223,7 @@
         <v>46239</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>46239</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68369,7 +68369,7 @@
         <v>46281</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68442,7 +68442,7 @@
         <v>45470</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68515,7 +68515,7 @@
         <v>46282</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68593,7 +68593,7 @@
         <v>44900</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68666,7 +68666,7 @@
         <v>46241</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68744,7 +68744,7 @@
         <v>46240</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68817,7 +68817,7 @@
         <v>46240</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68895,7 +68895,7 @@
         <v>46286</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68968,7 +68968,7 @@
         <v>45572</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69041,7 +69041,7 @@
         <v>45362</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69114,7 +69114,7 @@
         <v>46287</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69187,7 +69187,7 @@
         <v>44606</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69260,7 +69260,7 @@
         <v>46287</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69333,7 +69333,7 @@
         <v>46245</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69406,7 +69406,7 @@
         <v>46287</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>45226</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>44949</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45561</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>44610</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69776,7 +69776,7 @@
         <v>46287</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46287</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69932,7 +69932,7 @@
         <v>46287</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70010,7 +70010,7 @@
         <v>46244</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70083,7 +70083,7 @@
         <v>46244</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70156,7 +70156,7 @@
         <v>46244</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70229,7 +70229,7 @@
         <v>46245</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70302,7 +70302,7 @@
         <v>46245</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70380,7 +70380,7 @@
         <v>46286</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70453,7 +70453,7 @@
         <v>46287</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70526,7 +70526,7 @@
         <v>46246</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70599,7 +70599,7 @@
         <v>44679</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70672,7 +70672,7 @@
         <v>46246</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>46289</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>46290</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>45260</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>46247</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>45561</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>46246</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71188,7 +71188,7 @@
         <v>44740</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71261,7 +71261,7 @@
         <v>46247</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71334,7 +71334,7 @@
         <v>44620</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71407,7 +71407,7 @@
         <v>46248</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71480,7 +71480,7 @@
         <v>44839</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71553,7 +71553,7 @@
         <v>46289</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71626,7 +71626,7 @@
         <v>44727</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71699,7 +71699,7 @@
         <v>44981</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71772,7 +71772,7 @@
         <v>44944</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71845,7 +71845,7 @@
         <v>44944</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71918,7 +71918,7 @@
         <v>44652</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71991,7 +71991,7 @@
         <v>44944</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72064,7 +72064,7 @@
         <v>45154</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72137,7 +72137,7 @@
         <v>45309</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72215,7 +72215,7 @@
         <v>44980</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72293,7 +72293,7 @@
         <v>45042</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72366,7 +72366,7 @@
         <v>45208</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72439,7 +72439,7 @@
         <v>45597</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72517,7 +72517,7 @@
         <v>45247</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72590,7 +72590,7 @@
         <v>45030</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72663,7 +72663,7 @@
         <v>45078</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72736,7 +72736,7 @@
         <v>45635</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72814,7 +72814,7 @@
         <v>45401</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45692</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>45033</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73043,7 +73043,7 @@
         <v>45078</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73116,7 +73116,7 @@
         <v>45249</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73189,7 +73189,7 @@
         <v>45714</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73262,7 +73262,7 @@
         <v>45252</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73335,7 +73335,7 @@
         <v>45630</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73408,7 +73408,7 @@
         <v>44606</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73481,7 +73481,7 @@
         <v>44987</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73554,7 +73554,7 @@
         <v>45070</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73627,7 +73627,7 @@
         <v>45615</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73700,7 +73700,7 @@
         <v>45261</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73773,7 +73773,7 @@
         <v>45183</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73846,7 +73846,7 @@
         <v>44734</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73919,7 +73919,7 @@
         <v>45702</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73992,7 +73992,7 @@
         <v>45470</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74065,7 +74065,7 @@
         <v>44592</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74138,7 +74138,7 @@
         <v>45043</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74211,7 +74211,7 @@
         <v>45604</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74284,7 +74284,7 @@
         <v>44802</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74357,7 +74357,7 @@
         <v>45222</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74430,7 +74430,7 @@
         <v>45301</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74503,7 +74503,7 @@
         <v>45273</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74576,7 +74576,7 @@
         <v>45756</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74649,7 +74649,7 @@
         <v>45681</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74722,7 +74722,7 @@
         <v>45706</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74795,7 +74795,7 @@
         <v>45737</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74868,7 +74868,7 @@
         <v>45501</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -74941,7 +74941,7 @@
         <v>45616</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75014,7 +75014,7 @@
         <v>45722</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75087,7 +75087,7 @@
         <v>45749</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75160,7 +75160,7 @@
         <v>45604</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75233,7 +75233,7 @@
         <v>45630</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75306,7 +75306,7 @@
         <v>45530</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75384,7 +75384,7 @@
         <v>45530</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75457,7 +75457,7 @@
         <v>45260</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75530,7 +75530,7 @@
         <v>45540</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75603,7 +75603,7 @@
         <v>45747</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75676,7 +75676,7 @@
         <v>45636</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -75749,7 +75749,7 @@
         <v>45777</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45783</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -75900,7 +75900,7 @@
         <v>45783</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -75973,7 +75973,7 @@
         <v>45783</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>45785</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>45484</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76197,7 +76197,7 @@
         <v>45785</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76270,7 +76270,7 @@
         <v>45635</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76343,7 +76343,7 @@
         <v>45748</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76416,7 +76416,7 @@
         <v>45792</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76489,7 +76489,7 @@
         <v>45789</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76562,7 +76562,7 @@
         <v>45792</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76635,7 +76635,7 @@
         <v>45792</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -76708,7 +76708,7 @@
         <v>44726</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -76781,7 +76781,7 @@
         <v>44473</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -76859,7 +76859,7 @@
         <v>44482</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -76937,7 +76937,7 @@
         <v>45713</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77010,7 +77010,7 @@
         <v>45713</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77083,7 +77083,7 @@
         <v>46108</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77156,7 +77156,7 @@
         <v>46148</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77229,7 +77229,7 @@
         <v>46286</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>46038</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45579</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>45546</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45342</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45908</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>44772</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44868</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>44826</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44559</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45937</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45610</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44670</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45110</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>45523</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>45544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45264</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45562</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46182</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44925</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45019</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>46085</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45470</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45874</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45676</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>45195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>46275</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>45938</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45952</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>45952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>46104</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45831</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45695</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45873</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>46161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45160</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>46272</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>46282</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45993</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>46294</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>45965</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45562</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45250</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45434</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45940</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>46070</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44859</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45834</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45912</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>46093</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45993</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44543</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45684</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44673</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>46204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>46269</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>46027</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45567</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>46274</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45579</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45107</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44619</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45635</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45607</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44715</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44631</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44715</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45275</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>45099</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45488</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>46052</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45576</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45939</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45938</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>46078</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>46104</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45579</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>46113</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44944</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45723</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45470</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>46146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45840</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>46150</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>46150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>46155</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45343</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>44772</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>46182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45098</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>46195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>46202</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45426</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45120</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>46262</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45481</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>46269</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46272</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>45086</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>46283</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>46287</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45043</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44631</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45251</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45110</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45006</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45569</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44837</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>44931</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45624</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>46135</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44824</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44784</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>44788</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44652</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44777</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44489</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>44846</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44606</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44854</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44687</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44860</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>44841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>44813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44846</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>44859</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>44599</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44872</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>44802</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>44609</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44851</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44846</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44619</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>44599</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>44830</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44839</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44840</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44741</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44606</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44714</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44606</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44838</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44606</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>44475</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44533</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44581</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45418</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45037</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44840</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>45501</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45531</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>44944</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45630</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45470</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45211</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45681</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45681</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45567</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45524</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45037</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45484</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45252</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45670</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45104</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44818</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>45722</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45572</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45677</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45428</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44610</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45698</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45748</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45068</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45012</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46000</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45484</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45392</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45345</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>46006</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>46006</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>46006</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>45749</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>46006</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>46006</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44606</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45247</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45545</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46008</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45573</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46008</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45301</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45401</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>46013</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>46010</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46010</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45309</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45028</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45691</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>46014</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45022</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45345</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>46021</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46021</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46020</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44902</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>46027</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>44841</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45894</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45789</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45838</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>46029</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45761</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>46029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>46029</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45897</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44984</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>46031</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45897</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45898</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45901</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46034</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45901</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45803</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45792</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45604</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45792</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45904</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45749</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45904</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45904</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>46041</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46041</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>46038</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45909</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45775</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46043</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45792</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46043</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46044</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46044</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46044</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>46044</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45912</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45912</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45756</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45915</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45912</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45488</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45912</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44931</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45516</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>46049</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45632</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>46048</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45243</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>46049</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>46049</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45917</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45552</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45916</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46050</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44592</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45919</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45771</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>46050</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46050</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>46050</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44734</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45222</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45580</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>46052</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44679</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45923</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45923</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45922</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45925</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>45455</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45740</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44749</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45019</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45926</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45926</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45929</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45407</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45926</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>46059</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>46059</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45702</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45702</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46058</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46059</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45524</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44473</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45463</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45930</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>46063</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>44473</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45561</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>44980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>46064</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>46064</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>46064</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45932</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45933</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44574</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>46066</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45447</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>46069</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45938</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45938</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>46071</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45938</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45471</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>46071</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45939</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>46073</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45940</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45943</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>46073</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44483</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45811</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45944</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44917</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45559</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>45944</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45756</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45666</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45183</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>46078</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45946</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45951</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45237</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>45950</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45070</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>45951</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>45604</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45951</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45952</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45953</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45953</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45952</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45722</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45952</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45952</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45953</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45953</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>45952</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45953</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45952</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45952</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45957</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45957</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45957</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44740</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45957</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>45957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45957</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45957</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45957</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>46087</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>44606</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45959</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45958</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45623</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>44825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46091</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44847</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45940</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46091</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45646</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45769</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45635</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45966</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45966</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45041</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>46093</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45371</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>44619</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>44606</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46099</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46100</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>45202</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46100</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44620</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45972</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45189</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45091</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45091</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45975</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44515</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44774</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45975</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>44908</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>45975</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45975</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>46105</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45055</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45470</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45446</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>46105</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>46105</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46105</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46105</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>45356</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45980</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45439</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>46107</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45981</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45785</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>46107</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45985</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45348</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45982</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45462</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45982</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45646</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45586</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45986</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45824</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45825</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>46113</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45986</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45481</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45825</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45825</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45103</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>46120</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>46119</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>44983</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45989</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44511</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45824</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45824</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46122</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45992</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>46122</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45993</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>45992</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45540</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45993</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45993</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46126</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45091</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>44846</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44914</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>46001</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46000</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>46000</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45260</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45112</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>46001</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45833</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45832</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45883</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45399</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45722</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45120</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>44606</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44914</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45142</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45884</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>46041</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45838</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45840</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45447</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45826</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>44825</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45630</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>44900</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45478</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45469</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45842</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45938</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45846</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>44629</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45937</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44846</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45737</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45525</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>44820</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45923</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>44727</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45572</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45405</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45905</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45531</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45576</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45376</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45803</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45210</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45827</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45317</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>44987</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45316</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45714</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45812</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>44805</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45252</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45835</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>44740</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>46140</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44606</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>45709</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45709</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45711</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45866</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45405</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>46140</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46070</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45615</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>46141</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45253</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45868</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45965</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45432</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>44742</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>46141</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>44839</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45908</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45923</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45747</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45873</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45873</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46141</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>46141</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46141</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46146</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45173</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>46146</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45198</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>45790</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>46148</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45737</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45298</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>46153</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>46150</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45639</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45692</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45590</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>45681</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>45875</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>44920</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>46154</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>46154</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>45965</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>44628</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52455,7 +52455,7 @@
         <v>46155</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45273</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>46156</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45343</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>45167</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>46161</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>46161</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>46010</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>46048</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53112,7 +53112,7 @@
         <v>46161</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>46161</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         <v>45898</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>46160</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53409,7 +53409,7 @@
         <v>46161</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45875</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53560,7 +53560,7 @@
         <v>45874</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>46160</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>45876</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>46162</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45043</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>46167</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45120</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45876</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45505</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45877</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>46164</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>46167</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>46167</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>45488</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>46030</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>46167</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>46169</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>44944</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54904,7 +54904,7 @@
         <v>45641</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54977,7 +54977,7 @@
         <v>46168</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>46167</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55123,7 +55123,7 @@
         <v>46170</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55201,7 +55201,7 @@
         <v>45593</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45881</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46171</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45037</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         <v>44652</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
         <v>45082</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>44672</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>45692</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>46174</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>46008</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55941,7 +55941,7 @@
         <v>45041</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45427</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>46178</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         <v>46178</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45636</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>45016</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45226</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56477,7 +56477,7 @@
         <v>46177</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46177</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>46178</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45832</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45722</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45698</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         <v>46182</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>46182</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>46182</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>46182</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45741</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>45166</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>46183</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46183</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>46188</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46187</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>46185</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>46188</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>44839</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>46185</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>46185</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58050,7 +58050,7 @@
         <v>44900</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>44981</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45720</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>44840</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>46191</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>45140</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58498,7 +58498,7 @@
         <v>45771</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>46195</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58649,7 +58649,7 @@
         <v>45180</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>46195</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58795,7 +58795,7 @@
         <v>45042</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         <v>46195</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>46198</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59024,7 +59024,7 @@
         <v>44487</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59102,7 +59102,7 @@
         <v>45706</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
         <v>44790</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59248,7 +59248,7 @@
         <v>46198</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>44944</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59394,7 +59394,7 @@
         <v>46198</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45037</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>45569</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>45761</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>45301</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59774,7 +59774,7 @@
         <v>45078</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45106</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45687</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         <v>46205</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>46205</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60144,7 +60144,7 @@
         <v>46204</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         <v>45065</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>45441</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46205</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>45561</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45448</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60587,7 +60587,7 @@
         <v>45581</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>46205</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60738,7 +60738,7 @@
         <v>46205</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60816,7 +60816,7 @@
         <v>46205</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>46206</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         <v>46205</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45512</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>44594</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>46209</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45007</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>46211</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61425,7 +61425,7 @@
         <v>46212</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>46211</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61581,7 +61581,7 @@
         <v>46212</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61659,7 +61659,7 @@
         <v>45030</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61732,7 +61732,7 @@
         <v>46211</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61805,7 +61805,7 @@
         <v>46212</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>46259</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61961,7 +61961,7 @@
         <v>46259</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62039,7 +62039,7 @@
         <v>44949</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62112,7 +62112,7 @@
         <v>45623</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62185,7 +62185,7 @@
         <v>45174</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62263,7 +62263,7 @@
         <v>46259</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62336,7 +62336,7 @@
         <v>45572</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62409,7 +62409,7 @@
         <v>45194</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62487,7 +62487,7 @@
         <v>46259</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62560,7 +62560,7 @@
         <v>44873</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>46259</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>46213</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62789,7 +62789,7 @@
         <v>46259</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62867,7 +62867,7 @@
         <v>46213</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62945,7 +62945,7 @@
         <v>46259</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63023,7 +63023,7 @@
         <v>46259</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>46260</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63169,7 +63169,7 @@
         <v>46260</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45470</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63315,7 +63315,7 @@
         <v>45252</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63388,7 +63388,7 @@
         <v>45623</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>46262</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>46262</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63612,7 +63612,7 @@
         <v>46198</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63685,7 +63685,7 @@
         <v>46262</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63763,7 +63763,7 @@
         <v>46262</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>46262</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>46265</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>45670</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
         <v>45078</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>45616</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>45041</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>46269</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64367,7 +64367,7 @@
         <v>46269</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>46268</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>46269</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>46268</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64659,7 +64659,7 @@
         <v>45271</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45744</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>46269</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>45505</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64961,7 +64961,7 @@
         <v>46230</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>46195</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>46268</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65190,7 +65190,7 @@
         <v>46272</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65263,7 +65263,7 @@
         <v>46272</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65336,7 +65336,7 @@
         <v>46272</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65409,7 +65409,7 @@
         <v>46273</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65482,7 +65482,7 @@
         <v>45503</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>45385</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65633,7 +65633,7 @@
         <v>46274</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>45197</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65789,7 +65789,7 @@
         <v>44481</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65867,7 +65867,7 @@
         <v>46274</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65945,7 +65945,7 @@
         <v>46233</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66023,7 +66023,7 @@
         <v>46276</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>46276</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>46276</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>46276</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>46279</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>46280</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66476,7 +66476,7 @@
         <v>45208</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66549,7 +66549,7 @@
         <v>45455</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66622,7 +66622,7 @@
         <v>45113</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66695,7 +66695,7 @@
         <v>46281</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66768,7 +66768,7 @@
         <v>46280</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>46280</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66914,7 +66914,7 @@
         <v>46280</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66987,7 +66987,7 @@
         <v>45244</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67060,7 +67060,7 @@
         <v>46239</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67133,7 +67133,7 @@
         <v>45616</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         <v>45597</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67284,7 +67284,7 @@
         <v>45530</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67362,7 +67362,7 @@
         <v>45309</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67435,7 +67435,7 @@
         <v>46240</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67513,7 +67513,7 @@
         <v>45469</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67586,7 +67586,7 @@
         <v>46239</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67659,7 +67659,7 @@
         <v>46240</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67732,7 +67732,7 @@
         <v>45205</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67805,7 +67805,7 @@
         <v>46282</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67883,7 +67883,7 @@
         <v>46239</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67956,7 +67956,7 @@
         <v>45089</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68029,7 +68029,7 @@
         <v>45249</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68102,7 +68102,7 @@
         <v>45642</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68175,7 +68175,7 @@
         <v>46287</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68248,7 +68248,7 @@
         <v>45250</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>45572</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68394,7 +68394,7 @@
         <v>46287</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68472,7 +68472,7 @@
         <v>46286</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68545,7 +68545,7 @@
         <v>46287</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68618,7 +68618,7 @@
         <v>46286</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68691,7 +68691,7 @@
         <v>44939</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68764,7 +68764,7 @@
         <v>46244</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68837,7 +68837,7 @@
         <v>46287</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68910,7 +68910,7 @@
         <v>46287</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68988,7 +68988,7 @@
         <v>46287</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>46244</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69139,7 +69139,7 @@
         <v>46244</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69212,7 +69212,7 @@
         <v>45735</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69285,7 +69285,7 @@
         <v>45735</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69358,7 +69358,7 @@
         <v>46241</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69436,7 +69436,7 @@
         <v>46287</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69509,7 +69509,7 @@
         <v>45579</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69582,7 +69582,7 @@
         <v>46289</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45215</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69728,7 +69728,7 @@
         <v>45714</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69806,7 +69806,7 @@
         <v>46245</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69879,7 +69879,7 @@
         <v>46246</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69952,7 +69952,7 @@
         <v>46289</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70025,7 +70025,7 @@
         <v>46246</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>46245</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70181,7 +70181,7 @@
         <v>46248</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70254,7 +70254,7 @@
         <v>45426</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70327,7 +70327,7 @@
         <v>45392</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70400,7 +70400,7 @@
         <v>46293</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70473,7 +70473,7 @@
         <v>45708</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70551,7 +70551,7 @@
         <v>45531</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70624,7 +70624,7 @@
         <v>45199</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70697,7 +70697,7 @@
         <v>46293</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70770,7 +70770,7 @@
         <v>46247</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70843,7 +70843,7 @@
         <v>45629</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70916,7 +70916,7 @@
         <v>46247</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70989,7 +70989,7 @@
         <v>44873</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71062,7 +71062,7 @@
         <v>46290</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71135,7 +71135,7 @@
         <v>46183</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71208,7 +71208,7 @@
         <v>45230</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71281,7 +71281,7 @@
         <v>45755</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71354,7 +71354,7 @@
         <v>46295</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71427,7 +71427,7 @@
         <v>46294</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71500,7 +71500,7 @@
         <v>46294</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71573,7 +71573,7 @@
         <v>46251</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71646,7 +71646,7 @@
         <v>46294</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71719,7 +71719,7 @@
         <v>46252</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71792,7 +71792,7 @@
         <v>45013</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71865,7 +71865,7 @@
         <v>46251</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71943,7 +71943,7 @@
         <v>46295</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72016,7 +72016,7 @@
         <v>46252</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72089,7 +72089,7 @@
         <v>46252</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72167,7 +72167,7 @@
         <v>44805</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72245,7 +72245,7 @@
         <v>45539</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72318,7 +72318,7 @@
         <v>46252</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72391,7 +72391,7 @@
         <v>46294</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72469,7 +72469,7 @@
         <v>46251</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72542,7 +72542,7 @@
         <v>46251</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72615,7 +72615,7 @@
         <v>46251</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72688,7 +72688,7 @@
         <v>46294</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72766,7 +72766,7 @@
         <v>45225</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72839,7 +72839,7 @@
         <v>45167</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72917,7 +72917,7 @@
         <v>45940</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72990,7 +72990,7 @@
         <v>46297</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73063,7 +73063,7 @@
         <v>46254</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73136,7 +73136,7 @@
         <v>46255</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73209,7 +73209,7 @@
         <v>45244</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73282,7 +73282,7 @@
         <v>46254</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73355,7 +73355,7 @@
         <v>46297</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73428,7 +73428,7 @@
         <v>45471</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73506,7 +73506,7 @@
         <v>46254</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73579,7 +73579,7 @@
         <v>46161</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73657,7 +73657,7 @@
         <v>45478</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73730,7 +73730,7 @@
         <v>45706</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73803,7 +73803,7 @@
         <v>46252</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73876,7 +73876,7 @@
         <v>46245</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73949,7 +73949,7 @@
         <v>46246</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74022,7 +74022,7 @@
         <v>46297</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74095,7 +74095,7 @@
         <v>45009</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74168,7 +74168,7 @@
         <v>45033</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74246,7 +74246,7 @@
         <v>45047</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74319,7 +74319,7 @@
         <v>45714</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74397,7 +74397,7 @@
         <v>45099</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74475,7 +74475,7 @@
         <v>45111</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74548,7 +74548,7 @@
         <v>45594</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74621,7 +74621,7 @@
         <v>45706</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74694,7 +74694,7 @@
         <v>45440</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74767,7 +74767,7 @@
         <v>45530</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74845,7 +74845,7 @@
         <v>45544</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74918,7 +74918,7 @@
         <v>45040</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -74996,7 +74996,7 @@
         <v>45362</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75069,7 +75069,7 @@
         <v>45048</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75142,7 +75142,7 @@
         <v>45216</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75220,7 +75220,7 @@
         <v>45217</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75298,7 +75298,7 @@
         <v>45217</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75376,7 +75376,7 @@
         <v>44550</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75449,7 +75449,7 @@
         <v>45168</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75522,7 +75522,7 @@
         <v>45561</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75595,7 +75595,7 @@
         <v>44802</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75668,7 +75668,7 @@
         <v>45154</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75741,7 +75741,7 @@
         <v>45261</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -75814,7 +75814,7 @@
         <v>45484</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -75887,7 +75887,7 @@
         <v>45427</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -75960,7 +75960,7 @@
         <v>45741</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76033,7 +76033,7 @@
         <v>44715</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76106,7 +76106,7 @@
         <v>45260</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76179,7 +76179,7 @@
         <v>45755</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76252,7 +76252,7 @@
         <v>45616</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76325,7 +76325,7 @@
         <v>45636</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76398,7 +76398,7 @@
         <v>45033</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76471,7 +76471,7 @@
         <v>44937</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76544,7 +76544,7 @@
         <v>44480</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76617,7 +76617,7 @@
         <v>45530</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76690,7 +76690,7 @@
         <v>45777</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -76763,7 +76763,7 @@
         <v>45747</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -76836,7 +76836,7 @@
         <v>45636</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -76909,7 +76909,7 @@
         <v>45783</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -76987,7 +76987,7 @@
         <v>45783</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77065,7 +77065,7 @@
         <v>45783</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77138,7 +77138,7 @@
         <v>45785</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77211,7 +77211,7 @@
         <v>45785</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77284,7 +77284,7 @@
         <v>45635</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -77357,7 +77357,7 @@
         <v>44726</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -77430,7 +77430,7 @@
         <v>44473</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -77508,7 +77508,7 @@
         <v>44482</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -77586,7 +77586,7 @@
         <v>45713</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -77659,7 +77659,7 @@
         <v>45713</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -77732,7 +77732,7 @@
         <v>46108</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -77805,7 +77805,7 @@
         <v>46148</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -77878,7 +77878,7 @@
         <v>46286</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>46038</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45579</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>45546</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45342</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45908</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>44772</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44826</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>44868</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44559</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>46282</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45110</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45523</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45586</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>46286</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46294</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44715</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45544</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45562</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45264</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44925</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44645</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45581</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45676</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45019</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45470</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45874</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>46275</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>45734</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>45594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>45511</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>45562</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45160</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45938</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45952</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45873</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46104</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45695</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45831</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>46161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46272</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45965</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45993</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45250</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45434</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45940</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46070</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44859</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45834</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45635</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45912</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44619</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45567</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44673</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45684</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45579</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45847</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45803</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45019</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>46055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>46196</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>46204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>46269</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46274</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>46301</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>46027</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46027</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45762</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44715</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44631</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45099</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45426</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45624</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45749</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45481</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>44631</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44644</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45488</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44631</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45110</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45086</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45043</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45938</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45558</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45939</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45569</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>44904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44772</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44837</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45006</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45275</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>46104</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45579</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45723</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45576</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44944</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45470</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45098</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45147</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>46052</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45840</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>46146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46150</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>46150</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>46078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46155</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>46182</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>46202</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45120</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46272</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46269</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>46283</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>46287</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>46262</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>46135</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44824</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>44784</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44652</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44788</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44489</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44846</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44606</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44854</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44687</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44524</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44742</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>44841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44860</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44846</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44859</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44599</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44619</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44802</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44642</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44599</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44609</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44838</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44830</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44606</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44606</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44839</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44714</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44840</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44741</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44851</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44606</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>44846</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44533</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45030</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44581</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45755</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45078</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45469</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44790</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>44841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45418</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45091</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45635</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45082</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45401</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45440</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45692</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45714</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45033</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45427</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44846</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45078</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45298</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45249</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45376</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45525</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44873</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45103</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45089</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45106</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45405</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44825</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45714</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45252</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45448</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44481</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44846</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>44840</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45252</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44606</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45301</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45771</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44987</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45615</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45112</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>44480</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45261</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45183</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44734</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45702</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45385</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45371</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45463</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45113</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45470</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44592</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45037</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45604</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44802</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45222</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45503</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45301</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44874</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45392</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45455</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45140</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45573</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45455</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44515</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45273</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45681</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45471</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45253</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45636</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45446</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45706</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44873</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45737</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>44606</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45484</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45478</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45838</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45894</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45894</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45897</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45898</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45897</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45481</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44874</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45501</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45901</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45901</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45616</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45722</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45531</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45428</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45470</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44914</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45803</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45471</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45033</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45904</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45749</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45904</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45904</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45604</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45630</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45904</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45530</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45530</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45545</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45531</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45260</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45579</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45540</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45909</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45484</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45909</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45616</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45636</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45012</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45777</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45912</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45771</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45912</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45692</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>44984</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45912</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>45755</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45037</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45426</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45539</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45488</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45916</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45783</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45623</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45783</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45783</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45142</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45478</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45915</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44902</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45405</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45785</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45917</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45918</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45917</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44944</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45524</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45484</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45572</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45040</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45749</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45552</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44511</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45616</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45561</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>44574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45785</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45590</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45009</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45670</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45919</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45922</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45019</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45635</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45748</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45250</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45923</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45923</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45925</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45926</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45926</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45581</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45761</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45792</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45505</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45789</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45567</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>44594</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45926</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>45792</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44628</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>45636</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45642</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45028</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45047</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45929</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45516</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>44629</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44606</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45632</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45068</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45309</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45722</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>44550</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45243</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45932</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45048</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44937</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45933</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45702</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45244</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45356</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45399</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45677</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>45569</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45938</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45512</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45211</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45938</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45091</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45938</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45735</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45735</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45666</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45194</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45447</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>45691</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45237</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45940</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45939</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45939</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45811</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45407</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45623</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45594</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45943</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45944</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45629</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45166</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45708</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45709</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45709</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45711</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45769</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45392</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45439</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45950</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45099</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45348</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>44606</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45013</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45785</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45244</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45197</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>45687</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45824</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45441</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45681</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>44619</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45007</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45825</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45952</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45951</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45623</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45825</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45825</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45167</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45952</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45641</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45951</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45951</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>44487</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>44839</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45041</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45952</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45230</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45832</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45706</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>45952</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45741</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45198</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45952</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>44672</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45952</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45952</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45953</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45953</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45953</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45953</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45953</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45957</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>45957</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45957</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45957</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45957</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45957</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45958</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45957</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>45957</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45959</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45706</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45833</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>45180</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45639</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44805</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>45838</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45168</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45041</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45940</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45840</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45966</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45966</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45826</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>44749</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>44715</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45225</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45427</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45469</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45462</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45842</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>44900</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45720</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45215</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>45846</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>44774</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45972</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45189</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44740</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45722</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45174</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45975</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45975</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45531</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45803</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45217</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45217</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>44805</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45866</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44818</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>44742</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>44917</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>45868</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45975</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>44503</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45975</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45530</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45544</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45873</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45646</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45874</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45317</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45873</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45980</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45876</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45875</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45875</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>45876</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45877</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45740</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45982</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45981</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>44820</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45744</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45345</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>44488</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45881</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>45037</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45037</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45505</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45982</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45698</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45670</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45022</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>45986</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>46100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>46100</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45986</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45173</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>44840</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>46105</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>46105</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45167</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45216</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45741</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45985</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45205</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>46105</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>46105</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>46105</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45470</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>46107</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45720</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51882,7 +51882,7 @@
         <v>46107</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>44483</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52033,7 +52033,7 @@
         <v>45111</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45775</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>45714</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45761</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>45586</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45988</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45989</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45992</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45065</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>45572</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45992</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>45992</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45210</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>46113</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>44914</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>45993</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>46119</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>46120</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45993</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53528,7 +53528,7 @@
         <v>46122</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53601,7 +53601,7 @@
         <v>46122</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>45362</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>46000</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>46000</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>46000</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>46001</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>44606</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>46126</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45226</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>44949</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54341,7 +54341,7 @@
         <v>45561</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54414,7 +54414,7 @@
         <v>46001</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>44610</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>46006</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>46006</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>46006</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>46006</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>46006</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45883</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>46008</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>44679</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46008</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45260</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>45938</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45561</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>46010</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>46010</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45722</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>46013</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55743,7 +55743,7 @@
         <v>44740</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55816,7 +55816,7 @@
         <v>46014</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>46020</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>44620</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>44839</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56108,7 +56108,7 @@
         <v>45345</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>46021</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45884</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>46021</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45737</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>46027</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45937</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>46029</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>44727</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>46029</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>46029</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>44981</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>44944</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57057,7 +57057,7 @@
         <v>44944</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57130,7 +57130,7 @@
         <v>46029</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45905</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>45120</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>45447</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>46030</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>46034</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>44652</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>46140</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>46031</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>45572</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57865,7 +57865,7 @@
         <v>44944</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>46038</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46041</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>45316</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58157,7 +58157,7 @@
         <v>45154</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58230,7 +58230,7 @@
         <v>46041</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>45747</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46044</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>46044</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58527,7 +58527,7 @@
         <v>46044</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>46043</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>45309</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>46041</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>45827</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>44980</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>46044</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>45835</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45042</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>45908</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>46043</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45576</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59423,7 +59423,7 @@
         <v>45208</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59496,7 +59496,7 @@
         <v>46070</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59569,7 +59569,7 @@
         <v>46048</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>46140</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45923</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>45597</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>46050</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>46050</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60017,7 +60017,7 @@
         <v>46141</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60163,7 +60163,7 @@
         <v>45432</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60236,7 +60236,7 @@
         <v>45247</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60309,7 +60309,7 @@
         <v>46050</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         <v>45965</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>46141</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>46050</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>46049</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>46049</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45812</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60820,7 +60820,7 @@
         <v>46052</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60893,7 +60893,7 @@
         <v>46058</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>46059</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46059</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>46059</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46141</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>46141</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45923</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>45524</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>46141</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>46146</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61628,7 +61628,7 @@
         <v>45747</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>46064</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46064</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46146</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>46063</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>46064</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>46064</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45790</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>46066</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62290,7 +62290,7 @@
         <v>46148</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>46069</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>46150</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>46071</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>46071</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>46153</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>46154</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>46073</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>46073</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45559</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63030,7 +63030,7 @@
         <v>46154</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>46078</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>46155</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>44920</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>45965</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>46087</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>46156</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>46091</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>46091</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46160</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>45343</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>46160</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45898</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46161</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>46161</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>46093</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64218,7 +64218,7 @@
         <v>46162</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>46161</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>46161</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64437,7 +64437,7 @@
         <v>46161</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>46048</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64583,7 +64583,7 @@
         <v>46010</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>46164</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64734,7 +64734,7 @@
         <v>46168</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64807,7 +64807,7 @@
         <v>46167</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>46167</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64963,7 +64963,7 @@
         <v>46030</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65036,7 +65036,7 @@
         <v>46167</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65109,7 +65109,7 @@
         <v>46167</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65182,7 +65182,7 @@
         <v>46167</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65255,7 +65255,7 @@
         <v>45120</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65328,7 +65328,7 @@
         <v>45488</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>46169</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46170</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65562,7 +65562,7 @@
         <v>46171</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65640,7 +65640,7 @@
         <v>46174</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
         <v>45698</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65786,7 +65786,7 @@
         <v>46008</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>45832</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65932,7 +65932,7 @@
         <v>45016</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66010,7 +66010,7 @@
         <v>46177</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66083,7 +66083,7 @@
         <v>46177</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66161,7 +66161,7 @@
         <v>46178</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>46178</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66317,7 +66317,7 @@
         <v>46178</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66395,7 +66395,7 @@
         <v>46182</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66468,7 +66468,7 @@
         <v>46182</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66541,7 +66541,7 @@
         <v>46182</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66614,7 +66614,7 @@
         <v>46183</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66692,7 +66692,7 @@
         <v>46183</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46182</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46185</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66921,7 +66921,7 @@
         <v>46187</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>46185</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67072,7 +67072,7 @@
         <v>46185</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>46188</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67223,7 +67223,7 @@
         <v>46188</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67301,7 +67301,7 @@
         <v>46191</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>46195</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67452,7 +67452,7 @@
         <v>46195</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67525,7 +67525,7 @@
         <v>46195</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67603,7 +67603,7 @@
         <v>46198</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67681,7 +67681,7 @@
         <v>46198</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67754,7 +67754,7 @@
         <v>46198</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67827,7 +67827,7 @@
         <v>46205</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>46205</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67978,7 +67978,7 @@
         <v>46204</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68051,7 +68051,7 @@
         <v>46205</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68129,7 +68129,7 @@
         <v>46205</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68202,7 +68202,7 @@
         <v>46205</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68275,7 +68275,7 @@
         <v>46205</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>46205</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68431,7 +68431,7 @@
         <v>46209</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68509,7 +68509,7 @@
         <v>46206</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68582,7 +68582,7 @@
         <v>46211</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>46211</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68733,7 +68733,7 @@
         <v>46211</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68811,7 +68811,7 @@
         <v>46213</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68889,7 +68889,7 @@
         <v>46212</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68967,7 +68967,7 @@
         <v>46213</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>46212</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69123,7 +69123,7 @@
         <v>46212</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>46265</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46198</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>46268</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69420,7 +69420,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>46269</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69571,7 +69571,7 @@
         <v>46272</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69644,7 +69644,7 @@
         <v>46268</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69722,7 +69722,7 @@
         <v>46195</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69795,7 +69795,7 @@
         <v>46272</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>46272</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69941,7 +69941,7 @@
         <v>46269</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70014,7 +70014,7 @@
         <v>46269</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70087,7 +70087,7 @@
         <v>46269</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>46273</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70238,7 +70238,7 @@
         <v>46274</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70316,7 +70316,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70394,7 +70394,7 @@
         <v>46230</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70472,7 +70472,7 @@
         <v>46276</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70550,7 +70550,7 @@
         <v>46276</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70623,7 +70623,7 @@
         <v>46276</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70696,7 +70696,7 @@
         <v>46233</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70774,7 +70774,7 @@
         <v>46276</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>46280</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>46280</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71003,7 +71003,7 @@
         <v>46279</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>46280</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71149,7 +71149,7 @@
         <v>46280</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>46239</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>46239</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>46239</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71441,7 +71441,7 @@
         <v>46281</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71514,7 +71514,7 @@
         <v>46241</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71592,7 +71592,7 @@
         <v>46240</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71665,7 +71665,7 @@
         <v>46240</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71743,7 +71743,7 @@
         <v>46286</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71816,7 +71816,7 @@
         <v>45572</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71889,7 +71889,7 @@
         <v>46287</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71962,7 +71962,7 @@
         <v>46287</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72035,7 +72035,7 @@
         <v>46287</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72113,7 +72113,7 @@
         <v>46287</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>46287</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46244</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72342,7 +72342,7 @@
         <v>46244</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72415,7 +72415,7 @@
         <v>46244</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72488,7 +72488,7 @@
         <v>46245</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>46245</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72639,7 +72639,7 @@
         <v>46286</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72712,7 +72712,7 @@
         <v>46287</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72785,7 +72785,7 @@
         <v>46246</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>46289</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72936,7 +72936,7 @@
         <v>46290</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73009,7 +73009,7 @@
         <v>46247</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73082,7 +73082,7 @@
         <v>46246</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73155,7 +73155,7 @@
         <v>46247</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>46289</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73301,7 +73301,7 @@
         <v>46183</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73374,7 +73374,7 @@
         <v>46248</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73447,7 +73447,7 @@
         <v>46293</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>46293</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73593,7 +73593,7 @@
         <v>46294</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73671,7 +73671,7 @@
         <v>46294</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73744,7 +73744,7 @@
         <v>46294</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73817,7 +73817,7 @@
         <v>46294</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>46294</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73968,7 +73968,7 @@
         <v>46251</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>46251</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74114,7 +74114,7 @@
         <v>46251</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74187,7 +74187,7 @@
         <v>46251</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74260,7 +74260,7 @@
         <v>46251</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74338,7 +74338,7 @@
         <v>46252</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74411,7 +74411,7 @@
         <v>46252</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74484,7 +74484,7 @@
         <v>46252</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74557,7 +74557,7 @@
         <v>46295</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74630,7 +74630,7 @@
         <v>46252</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>46295</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74781,7 +74781,7 @@
         <v>46255</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74854,7 +74854,7 @@
         <v>45940</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>46297</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46246</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>46254</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75146,7 +75146,7 @@
         <v>46254</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75219,7 +75219,7 @@
         <v>46161</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>46297</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>46300</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75448,7 +75448,7 @@
         <v>46252</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75521,7 +75521,7 @@
         <v>46297</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75594,7 +75594,7 @@
         <v>46254</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75667,7 +75667,7 @@
         <v>46245</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75740,7 +75740,7 @@
         <v>46301</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -75813,7 +75813,7 @@
         <v>46259</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -75886,7 +75886,7 @@
         <v>46259</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -75964,7 +75964,7 @@
         <v>46259</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>46259</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76115,7 +76115,7 @@
         <v>46301</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>46301</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76261,7 +76261,7 @@
         <v>46259</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76339,7 +76339,7 @@
         <v>46302</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76412,7 +76412,7 @@
         <v>46259</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76485,7 +76485,7 @@
         <v>46301</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76558,7 +76558,7 @@
         <v>46259</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>46259</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76714,7 +76714,7 @@
         <v>46304</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -76787,7 +76787,7 @@
         <v>46303</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -76860,7 +76860,7 @@
         <v>46262</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -76933,7 +76933,7 @@
         <v>46260</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77006,7 +77006,7 @@
         <v>46303</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77079,7 +77079,7 @@
         <v>46262</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77157,7 +77157,7 @@
         <v>46262</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77235,7 +77235,7 @@
         <v>46304</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77308,7 +77308,7 @@
         <v>45681</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -77381,7 +77381,7 @@
         <v>46287</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -77454,7 +77454,7 @@
         <v>46304</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -77527,7 +77527,7 @@
         <v>46262</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         <v>46262</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -77683,7 +77683,7 @@
         <v>46260</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -77756,7 +77756,7 @@
         <v>46304</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -77829,7 +77829,7 @@
         <v>45993</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -77902,7 +77902,7 @@
         <v>44726</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -77975,7 +77975,7 @@
         <v>44482</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78053,7 +78053,7 @@
         <v>45713</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78126,7 +78126,7 @@
         <v>45713</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>46108</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78272,7 +78272,7 @@
         <v>46148</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -78345,7 +78345,7 @@
         <v>46286</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>46038</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45579</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>45546</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45342</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45908</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>44772</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44826</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>44868</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44559</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>46282</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45110</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45523</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45586</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>46286</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46294</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44715</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45544</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45562</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45264</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44925</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44645</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45581</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45676</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45019</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45470</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45874</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>46275</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>45734</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>45594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>45511</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>45562</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45160</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45938</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45952</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45873</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46104</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45695</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45831</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>46161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46272</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45965</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45993</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45250</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45434</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45940</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46070</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44859</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45834</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45635</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45912</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44619</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45567</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44673</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45684</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45579</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45847</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45803</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45019</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>46055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>46164</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>46196</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>46204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>46269</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46274</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>46301</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>46027</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46027</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45762</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44715</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44631</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45099</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45426</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45624</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45749</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45481</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>44631</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44644</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45488</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44631</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45110</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45086</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45043</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45938</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45558</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45939</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45569</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>44904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44772</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44837</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45006</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45275</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>46104</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45579</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45723</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45576</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44944</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45470</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45098</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45147</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>46052</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45840</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>46146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46150</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>46150</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>46078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46155</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>46182</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>46202</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45120</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46272</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46269</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>46283</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>46287</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>46262</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>46135</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44824</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>44784</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44652</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44788</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44489</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44846</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44606</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44854</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44687</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44524</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44742</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>44841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44860</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44846</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44859</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44599</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44619</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44802</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44642</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44599</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44609</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44838</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44830</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44606</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44606</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44839</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44714</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44840</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44741</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44851</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44606</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>44846</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44533</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45030</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44581</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45755</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45078</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45469</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44790</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>44841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45418</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45091</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45635</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45082</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45401</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45440</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45692</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45714</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45033</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45427</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44846</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45078</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45298</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45249</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45376</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45525</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44873</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45103</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45089</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45106</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45405</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44825</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45714</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45252</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45448</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44481</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44846</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>44840</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45252</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44606</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45301</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45771</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44987</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45615</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45112</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>44480</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45261</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45183</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44734</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45702</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45385</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45371</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45463</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45113</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45470</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44592</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45037</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45604</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44802</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45222</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45503</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45301</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44874</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45392</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45455</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45140</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45573</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45455</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44515</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45273</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45681</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45471</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45253</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45636</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45446</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45706</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44873</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45737</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>44606</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45484</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45478</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45838</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45894</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45894</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45897</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45898</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45897</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45481</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44874</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45501</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45901</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45901</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45616</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45722</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45531</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45428</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45470</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44914</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45803</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45471</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45033</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45904</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45749</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45904</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45904</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45604</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45630</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45904</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45530</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45530</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45545</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45531</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45260</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45579</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45540</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45909</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45484</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45909</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45616</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45636</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45012</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45777</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45912</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45771</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45912</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45692</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>44984</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45912</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>45755</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45037</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45426</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45539</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45488</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45916</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45783</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45623</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45783</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45783</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45142</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45478</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45915</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44902</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45405</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45785</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45917</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45918</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45917</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44944</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45524</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45484</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45572</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45040</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45749</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45552</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44511</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45616</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45561</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>44574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45785</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45590</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45009</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45670</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45919</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45922</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45019</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45635</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45748</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45250</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45923</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45923</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45925</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45926</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45926</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45581</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45761</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45792</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45505</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45789</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45567</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>44594</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45926</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>45792</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44628</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>45636</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45642</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45028</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45047</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45929</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45516</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>44629</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44606</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45632</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45068</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45309</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45722</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>44550</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45243</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45932</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45048</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44937</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45933</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45702</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45244</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45356</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45399</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45677</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>45569</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45938</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45512</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45211</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45938</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45091</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45938</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45735</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45735</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45666</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45194</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45447</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>45691</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45237</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45940</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45939</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45939</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45811</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45407</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45623</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45594</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45943</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45944</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45629</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45166</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45708</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45709</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45709</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45711</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45769</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45392</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45439</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45950</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45099</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45348</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>44606</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45013</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45785</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45244</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45197</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>45687</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45824</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45441</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45681</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>44619</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45007</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45825</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45952</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45951</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45623</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45825</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45825</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45167</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45952</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45641</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45951</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45951</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>44487</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>44839</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45041</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45952</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45230</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45832</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45706</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>45952</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45741</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45198</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45952</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>44672</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45952</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45952</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45953</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45953</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45953</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45953</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45953</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45957</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>45957</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45957</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45957</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45957</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45957</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45958</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45957</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>45957</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45959</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45706</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45833</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>45180</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45639</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44805</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>45838</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45168</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45041</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45940</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45840</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45966</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45966</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45826</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>44749</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>44715</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45225</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45427</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45469</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45462</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45842</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>44900</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45720</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45215</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>45846</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>44774</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45972</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45189</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44740</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45722</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45174</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45975</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45975</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45531</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45803</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45217</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45217</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>44805</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45866</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44818</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>44742</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>44917</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>45868</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45975</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>44503</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45975</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45530</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45544</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45873</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45646</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45874</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45317</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45873</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45980</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45876</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45875</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45875</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>45876</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45877</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45740</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45982</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45981</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>44820</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45744</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45345</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>44488</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45881</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>45037</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45037</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45505</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45982</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45698</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45670</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45022</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>45986</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>46100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>46100</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45986</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45173</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>44840</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>46105</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>46105</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45167</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45216</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45741</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45985</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45205</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>46105</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>46105</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>46105</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45470</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>46107</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45720</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51882,7 +51882,7 @@
         <v>46107</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>44483</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52033,7 +52033,7 @@
         <v>45111</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45775</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>45714</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45761</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>45586</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45988</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45989</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45992</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45065</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>45572</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45992</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>45992</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45210</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>46113</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>44914</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>45993</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>46119</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>46120</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45993</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53528,7 +53528,7 @@
         <v>46122</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53601,7 +53601,7 @@
         <v>46122</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>45362</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>46000</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>46000</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>46000</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>46001</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>44606</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>46126</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45226</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>44949</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54341,7 +54341,7 @@
         <v>45561</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54414,7 +54414,7 @@
         <v>46001</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>44610</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>46006</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>46006</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>46006</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>46006</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>46006</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45883</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>46008</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>44679</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46008</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45260</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>45938</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45561</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>46010</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>46010</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45722</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>46013</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55743,7 +55743,7 @@
         <v>44740</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55816,7 +55816,7 @@
         <v>46014</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>46020</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>44620</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>44839</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56108,7 +56108,7 @@
         <v>45345</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>46021</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45884</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>46021</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45737</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>46027</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45937</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>46029</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>44727</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>46029</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>46029</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>44981</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>44944</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57057,7 +57057,7 @@
         <v>44944</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57130,7 +57130,7 @@
         <v>46029</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45905</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>45120</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>45447</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>46030</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>46034</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>44652</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>46140</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>46031</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>45572</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57865,7 +57865,7 @@
         <v>44944</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>46038</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46041</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>45316</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58157,7 +58157,7 @@
         <v>45154</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58230,7 +58230,7 @@
         <v>46041</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>45747</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46044</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>46044</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58527,7 +58527,7 @@
         <v>46044</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>46043</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>45309</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>46041</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>45827</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>44980</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>46044</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>45835</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45042</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>45908</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>46043</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45576</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59423,7 +59423,7 @@
         <v>45208</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59496,7 +59496,7 @@
         <v>46070</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59569,7 +59569,7 @@
         <v>46048</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>46140</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45923</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>45597</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>46050</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>46050</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60017,7 +60017,7 @@
         <v>46141</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60163,7 +60163,7 @@
         <v>45432</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60236,7 +60236,7 @@
         <v>45247</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60309,7 +60309,7 @@
         <v>46050</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         <v>45965</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>46141</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>46050</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>46049</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>46049</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45812</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60820,7 +60820,7 @@
         <v>46052</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60893,7 +60893,7 @@
         <v>46058</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>46059</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46059</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>46059</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46141</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>46141</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45923</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>45524</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>46141</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>46146</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61628,7 +61628,7 @@
         <v>45747</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>46064</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46064</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46146</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>46063</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>46064</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>46064</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45790</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>46066</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62290,7 +62290,7 @@
         <v>46148</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>46069</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>46150</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>46071</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>46071</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>46153</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>46154</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>46073</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>46073</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45559</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63030,7 +63030,7 @@
         <v>46154</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>46078</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>46155</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>44920</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>45965</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>46087</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>46156</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>46091</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>46091</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46160</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>45343</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>46160</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45898</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46161</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>46161</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>46093</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64218,7 +64218,7 @@
         <v>46162</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>46161</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>46161</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64437,7 +64437,7 @@
         <v>46161</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>46048</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64583,7 +64583,7 @@
         <v>46010</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>46164</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64734,7 +64734,7 @@
         <v>46168</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64807,7 +64807,7 @@
         <v>46167</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>46167</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64963,7 +64963,7 @@
         <v>46030</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65036,7 +65036,7 @@
         <v>46167</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65109,7 +65109,7 @@
         <v>46167</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65182,7 +65182,7 @@
         <v>46167</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65255,7 +65255,7 @@
         <v>45120</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65328,7 +65328,7 @@
         <v>45488</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>46169</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>46170</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65562,7 +65562,7 @@
         <v>46171</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65640,7 +65640,7 @@
         <v>46174</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
         <v>45698</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65786,7 +65786,7 @@
         <v>46008</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>45832</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65932,7 +65932,7 @@
         <v>45016</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66010,7 +66010,7 @@
         <v>46177</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66083,7 +66083,7 @@
         <v>46177</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66161,7 +66161,7 @@
         <v>46178</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>46178</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66317,7 +66317,7 @@
         <v>46178</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66395,7 +66395,7 @@
         <v>46182</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66468,7 +66468,7 @@
         <v>46182</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66541,7 +66541,7 @@
         <v>46182</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66614,7 +66614,7 @@
         <v>46183</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66692,7 +66692,7 @@
         <v>46183</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46182</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46185</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66921,7 +66921,7 @@
         <v>46187</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>46185</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67072,7 +67072,7 @@
         <v>46185</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>46188</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67223,7 +67223,7 @@
         <v>46188</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67301,7 +67301,7 @@
         <v>46191</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>46195</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67452,7 +67452,7 @@
         <v>46195</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67525,7 +67525,7 @@
         <v>46195</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67603,7 +67603,7 @@
         <v>46198</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67681,7 +67681,7 @@
         <v>46198</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67754,7 +67754,7 @@
         <v>46198</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67827,7 +67827,7 @@
         <v>46205</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>46205</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67978,7 +67978,7 @@
         <v>46204</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68051,7 +68051,7 @@
         <v>46205</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68129,7 +68129,7 @@
         <v>46205</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68202,7 +68202,7 @@
         <v>46205</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68275,7 +68275,7 @@
         <v>46205</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>46205</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68431,7 +68431,7 @@
         <v>46209</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68509,7 +68509,7 @@
         <v>46206</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68582,7 +68582,7 @@
         <v>46211</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>46211</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68733,7 +68733,7 @@
         <v>46211</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68811,7 +68811,7 @@
         <v>46213</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68889,7 +68889,7 @@
         <v>46212</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68967,7 +68967,7 @@
         <v>46213</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>46212</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69123,7 +69123,7 @@
         <v>46212</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>46265</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46198</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>46268</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69420,7 +69420,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>46269</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69571,7 +69571,7 @@
         <v>46272</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69644,7 +69644,7 @@
         <v>46268</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69722,7 +69722,7 @@
         <v>46195</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69795,7 +69795,7 @@
         <v>46272</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>46272</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69941,7 +69941,7 @@
         <v>46269</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70014,7 +70014,7 @@
         <v>46269</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70087,7 +70087,7 @@
         <v>46269</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>46273</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70238,7 +70238,7 @@
         <v>46274</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70316,7 +70316,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70394,7 +70394,7 @@
         <v>46230</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70472,7 +70472,7 @@
         <v>46276</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70550,7 +70550,7 @@
         <v>46276</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70623,7 +70623,7 @@
         <v>46276</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70696,7 +70696,7 @@
         <v>46233</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70774,7 +70774,7 @@
         <v>46276</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>46280</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>46280</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71003,7 +71003,7 @@
         <v>46279</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>46280</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71149,7 +71149,7 @@
         <v>46280</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>46239</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>46239</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>46239</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71441,7 +71441,7 @@
         <v>46281</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71514,7 +71514,7 @@
         <v>46241</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71592,7 +71592,7 @@
         <v>46240</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71665,7 +71665,7 @@
         <v>46240</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71743,7 +71743,7 @@
         <v>46286</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71816,7 +71816,7 @@
         <v>45572</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71889,7 +71889,7 @@
         <v>46287</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71962,7 +71962,7 @@
         <v>46287</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72035,7 +72035,7 @@
         <v>46287</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72113,7 +72113,7 @@
         <v>46287</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>46287</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46244</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72342,7 +72342,7 @@
         <v>46244</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72415,7 +72415,7 @@
         <v>46244</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72488,7 +72488,7 @@
         <v>46245</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>46245</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72639,7 +72639,7 @@
         <v>46286</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72712,7 +72712,7 @@
         <v>46287</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72785,7 +72785,7 @@
         <v>46246</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>46289</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72936,7 +72936,7 @@
         <v>46290</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73009,7 +73009,7 @@
         <v>46247</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73082,7 +73082,7 @@
         <v>46246</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73155,7 +73155,7 @@
         <v>46247</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>46289</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73301,7 +73301,7 @@
         <v>46183</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73374,7 +73374,7 @@
         <v>46248</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73447,7 +73447,7 @@
         <v>46293</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>46293</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73593,7 +73593,7 @@
         <v>46294</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73671,7 +73671,7 @@
         <v>46294</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73744,7 +73744,7 @@
         <v>46294</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73817,7 +73817,7 @@
         <v>46294</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>46294</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73968,7 +73968,7 @@
         <v>46251</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>46251</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74114,7 +74114,7 @@
         <v>46251</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74187,7 +74187,7 @@
         <v>46251</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74260,7 +74260,7 @@
         <v>46251</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74338,7 +74338,7 @@
         <v>46252</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74411,7 +74411,7 @@
         <v>46252</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74484,7 +74484,7 @@
         <v>46252</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74557,7 +74557,7 @@
         <v>46295</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74630,7 +74630,7 @@
         <v>46252</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>46295</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74781,7 +74781,7 @@
         <v>46255</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74854,7 +74854,7 @@
         <v>45940</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>46297</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46246</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>46254</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75146,7 +75146,7 @@
         <v>46254</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75219,7 +75219,7 @@
         <v>46161</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>46297</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>46300</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75448,7 +75448,7 @@
         <v>46252</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75521,7 +75521,7 @@
         <v>46297</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75594,7 +75594,7 @@
         <v>46254</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75667,7 +75667,7 @@
         <v>46245</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75740,7 +75740,7 @@
         <v>46301</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -75813,7 +75813,7 @@
         <v>46259</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -75886,7 +75886,7 @@
         <v>46259</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -75964,7 +75964,7 @@
         <v>46259</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>46259</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76115,7 +76115,7 @@
         <v>46301</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>46301</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76261,7 +76261,7 @@
         <v>46259</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76339,7 +76339,7 @@
         <v>46302</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76412,7 +76412,7 @@
         <v>46259</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76485,7 +76485,7 @@
         <v>46301</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76558,7 +76558,7 @@
         <v>46259</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>46259</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76714,7 +76714,7 @@
         <v>46304</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -76787,7 +76787,7 @@
         <v>46303</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -76860,7 +76860,7 @@
         <v>46262</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -76933,7 +76933,7 @@
         <v>46260</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77006,7 +77006,7 @@
         <v>46303</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77079,7 +77079,7 @@
         <v>46262</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77157,7 +77157,7 @@
         <v>46262</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77235,7 +77235,7 @@
         <v>46304</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77308,7 +77308,7 @@
         <v>45681</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -77381,7 +77381,7 @@
         <v>46287</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -77454,7 +77454,7 @@
         <v>46304</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -77527,7 +77527,7 @@
         <v>46262</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         <v>46262</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -77683,7 +77683,7 @@
         <v>46260</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -77756,7 +77756,7 @@
         <v>46304</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -77829,7 +77829,7 @@
         <v>45993</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -77902,7 +77902,7 @@
         <v>44726</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -77975,7 +77975,7 @@
         <v>44482</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78053,7 +78053,7 @@
         <v>45713</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78126,7 +78126,7 @@
         <v>45713</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>46108</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78272,7 +78272,7 @@
         <v>46148</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -78345,7 +78345,7 @@
         <v>46286</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>46038</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45579</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>45342</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45546</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45579</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45908</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>44772</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44826</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>44868</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44559</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>46282</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46286</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45523</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44715</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45723</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44925</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44645</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>46182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45562</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45581</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45264</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>46070</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45676</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46085</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45470</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>46275</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45019</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45938</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45952</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>46282</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>46104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>45873</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45562</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45695</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45831</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>46272</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45993</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45965</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45250</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45434</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45940</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44859</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44566</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45834</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45912</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>45019</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>46204</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45635</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>46055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>46093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45847</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46027</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>46027</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44619</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46269</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45567</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>46274</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>46155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45579</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44543</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45684</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45607</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45762</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44715</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44944</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45098</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45147</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45939</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46182</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>46202</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45120</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45426</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45624</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45749</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46283</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45488</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46287</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46052</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45558</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>46078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>46104</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>46308</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46308</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>46262</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46309</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44631</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46269</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>46314</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>46314</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45470</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46314</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>46272</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44644</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44631</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45840</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46275</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45086</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>46150</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46150</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>45569</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44837</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45099</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45481</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45110</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45043</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44772</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45275</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45576</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46135</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44824</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44587</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44784</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44652</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44777</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44846</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44606</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44854</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44687</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44524</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44742</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44841</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44813</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44846</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44859</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44599</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44872</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44802</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44609</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44851</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44846</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44619</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>44599</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>44830</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44588</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>44839</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44840</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44741</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44606</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44714</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>44846</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44606</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44838</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44606</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>44631</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44533</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44581</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45714</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45636</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44679</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45838</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45405</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>44825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44846</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45897</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45771</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45898</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45561</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45901</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45901</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>44620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45803</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45904</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45904</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45904</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44839</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45904</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>46160</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45898</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46161</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>46161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45909</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46162</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46161</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46161</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>46161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45912</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>46048</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45912</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45912</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44944</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44944</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>46010</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45916</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>46164</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44652</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>45915</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45918</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45917</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45552</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46168</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44944</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45919</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46167</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45922</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45923</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46030</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45154</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45923</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45925</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45926</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45926</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46167</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>44790</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46167</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45120</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45488</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45309</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>44980</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44841</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46169</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45930</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45418</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45929</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45091</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45091</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45932</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46171</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45208</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45933</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45597</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45938</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45247</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45940</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45939</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45030</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45944</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45944</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45427</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45943</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44846</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45078</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45698</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46008</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45832</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45016</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46177</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45448</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45635</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>44840</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45252</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45946</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45401</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45301</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45692</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46177</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46178</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46178</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45950</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45033</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45078</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45952</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>45951</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45951</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45951</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45249</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45952</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45952</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45952</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46182</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45952</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45952</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>46182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45953</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45953</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>46182</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45953</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45953</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>46183</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45714</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46183</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45252</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45957</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45957</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>46187</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45957</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>46185</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45957</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45630</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44606</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46185</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45959</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>44987</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>45070</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45615</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>46188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45940</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>46188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>46191</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45261</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45183</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45702</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>46195</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>46195</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45972</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46195</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45470</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>44592</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45043</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45975</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45975</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45604</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44802</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46198</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45222</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45975</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>45301</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>46198</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46198</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45980</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45273</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45982</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45981</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45463</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>46205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45756</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45681</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45982</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45706</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46205</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45737</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>45986</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46205</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46205</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45985</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46206</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45501</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45586</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45988</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45722</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>46211</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>46211</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45989</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45992</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46211</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45992</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>46213</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>46212</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46213</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45993</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>46212</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45749</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45037</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45604</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45630</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>45530</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45530</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45593</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45260</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45540</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45503</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45747</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>46000</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>46001</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45636</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46198</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>45777</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>46001</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>46006</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>46006</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>46195</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46006</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46006</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>46006</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45783</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>46008</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>46230</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45785</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>46233</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>46008</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46280</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46010</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46010</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45484</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46280</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>46013</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45785</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>46279</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>46280</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>46014</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>46239</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46020</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>46239</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45635</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>46239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45345</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>46281</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>46021</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46021</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46027</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46029</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45792</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46029</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46029</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46241</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45789</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45792</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>46240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>46034</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45455</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45792</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>46031</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>46286</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45572</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45140</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>46038</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45573</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>46287</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>46041</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45632</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>46041</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>46044</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46044</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>46044</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45243</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>46043</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>46287</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>46044</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>46287</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>46287</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>46287</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46244</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>46244</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>46244</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>46048</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>46245</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>46245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>46286</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>46287</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>46050</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>46050</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>46049</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>46050</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>46050</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>46049</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>46049</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>46246</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>46052</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>46289</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>46290</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>46247</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>46246</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45666</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>46247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>46058</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45447</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46289</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46059</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46059</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45237</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>46183</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>46059</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45524</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45811</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45623</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46248</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>46064</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>46293</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>46064</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>46063</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>46293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>46294</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>46064</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>46064</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46294</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46294</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45769</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>46066</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45439</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>46294</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>46294</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>46069</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>46071</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45471</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>46251</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45785</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45446</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>46071</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45824</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45824</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46073</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45824</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46073</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45559</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>46251</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>46251</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>46252</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45825</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>46078</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45825</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45825</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>46252</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>46252</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>46295</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>46252</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>46295</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>44873</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45832</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>46255</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45940</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45833</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>46087</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>46297</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>46246</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>46091</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45838</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46091</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>46254</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>46254</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53361,7 +53361,7 @@
         <v>46161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>46297</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>46093</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>44606</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45840</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46300</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53809,7 +53809,7 @@
         <v>45484</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         <v>46252</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45826</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>46297</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54101,7 +54101,7 @@
         <v>45842</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>46254</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45846</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>46100</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>46100</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54466,7 +54466,7 @@
         <v>46099</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45478</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>46245</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45481</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46105</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46105</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54904,7 +54904,7 @@
         <v>46301</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54977,7 +54977,7 @@
         <v>46259</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>46259</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>44874</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55206,7 +55206,7 @@
         <v>46259</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>46105</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46105</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55425,7 +55425,7 @@
         <v>46105</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55498,7 +55498,7 @@
         <v>46107</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
         <v>46259</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>46107</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>46301</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>46301</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>46259</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>46302</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>46259</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>45531</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>45531</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>46301</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>45803</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>46259</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>46113</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56550,7 +56550,7 @@
         <v>46259</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>46304</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>45866</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45428</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45470</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         <v>46303</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>45868</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>46119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45471</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>46120</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45033</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>46260</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46303</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45873</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46304</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>45874</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>46122</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>46304</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46122</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>45873</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>46260</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58113,7 +58113,7 @@
         <v>46304</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45876</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>45875</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58337,7 +58337,7 @@
         <v>46126</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>45875</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>45876</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46262</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>46308</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45877</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>46265</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58853,7 +58853,7 @@
         <v>46262</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>46262</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>46262</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>45681</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59160,7 +59160,7 @@
         <v>45545</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>45881</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45484</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59379,7 +59379,7 @@
         <v>45993</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59452,7 +59452,7 @@
         <v>45539</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>44939</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>45883</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46307</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>44902</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>45405</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59895,7 +59895,7 @@
         <v>46310</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>46309</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>46309</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>45938</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>46309</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60265,7 +60265,7 @@
         <v>44944</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>46310</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>45524</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60484,7 +60484,7 @@
         <v>46310</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45749</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>45722</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         <v>45561</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>44574</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60849,7 +60849,7 @@
         <v>45884</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45009</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60995,7 +60995,7 @@
         <v>45737</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61068,7 +61068,7 @@
         <v>45937</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61141,7 +61141,7 @@
         <v>45019</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>46314</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45905</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>45120</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45447</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>46268</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>46269</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61672,7 +61672,7 @@
         <v>46314</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61745,7 +61745,7 @@
         <v>46140</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>45581</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61891,7 +61891,7 @@
         <v>46262</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61969,7 +61969,7 @@
         <v>45572</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62042,7 +62042,7 @@
         <v>46269</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>46269</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62188,7 +62188,7 @@
         <v>46268</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62266,7 +62266,7 @@
         <v>46269</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62344,7 +62344,7 @@
         <v>46268</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45505</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45567</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>46316</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>46273</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62709,7 +62709,7 @@
         <v>46272</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62782,7 +62782,7 @@
         <v>45636</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62855,7 +62855,7 @@
         <v>45316</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62928,7 +62928,7 @@
         <v>45747</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63001,7 +63001,7 @@
         <v>46315</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>46041</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63147,7 +63147,7 @@
         <v>45827</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>46315</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63293,7 +63293,7 @@
         <v>45835</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63371,7 +63371,7 @@
         <v>46316</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>46272</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45908</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>45047</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>46272</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63736,7 +63736,7 @@
         <v>45576</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63814,7 +63814,7 @@
         <v>46070</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>44629</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>44606</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64033,7 +64033,7 @@
         <v>46140</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64111,7 +64111,7 @@
         <v>45923</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>45722</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>46274</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64335,7 +64335,7 @@
         <v>46318</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64413,7 +64413,7 @@
         <v>46318</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>46318</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>46141</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64642,7 +64642,7 @@
         <v>46276</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45432</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64793,7 +64793,7 @@
         <v>46276</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64871,7 +64871,7 @@
         <v>45965</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64944,7 +64944,7 @@
         <v>46141</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>44937</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65090,7 +65090,7 @@
         <v>46276</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65163,7 +65163,7 @@
         <v>45812</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65236,7 +65236,7 @@
         <v>46276</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65309,7 +65309,7 @@
         <v>46141</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>45702</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>46141</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>45923</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>46141</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>44983</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>45244</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65825,7 +65825,7 @@
         <v>46146</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65898,7 +65898,7 @@
         <v>45747</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65971,7 +65971,7 @@
         <v>46274</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>45756</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>46146</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66200,7 +66200,7 @@
         <v>46281</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66273,7 +66273,7 @@
         <v>46287</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66346,7 +66346,7 @@
         <v>45790</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66419,7 +66419,7 @@
         <v>45399</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66492,7 +66492,7 @@
         <v>46148</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>45211</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>46150</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66721,7 +66721,7 @@
         <v>46153</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66794,7 +66794,7 @@
         <v>46154</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66867,7 +66867,7 @@
         <v>46154</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66940,7 +66940,7 @@
         <v>45594</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67013,7 +67013,7 @@
         <v>46155</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67086,7 +67086,7 @@
         <v>45271</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67159,7 +67159,7 @@
         <v>45629</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67232,7 +67232,7 @@
         <v>44920</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67305,7 +67305,7 @@
         <v>45965</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67378,7 +67378,7 @@
         <v>46156</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45348</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67529,7 +67529,7 @@
         <v>45013</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>46160</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67680,7 +67680,7 @@
         <v>45343</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67753,7 +67753,7 @@
         <v>45244</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67826,7 +67826,7 @@
         <v>45580</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67899,7 +67899,7 @@
         <v>45007</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45623</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         <v>45641</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68123,7 +68123,7 @@
         <v>45041</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68201,7 +68201,7 @@
         <v>45041</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68279,7 +68279,7 @@
         <v>45706</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68352,7 +68352,7 @@
         <v>45639</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68425,7 +68425,7 @@
         <v>44805</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68503,7 +68503,7 @@
         <v>45041</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68576,7 +68576,7 @@
         <v>44715</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68649,7 +68649,7 @@
         <v>45427</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68722,7 +68722,7 @@
         <v>44900</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68795,7 +68795,7 @@
         <v>44774</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68868,7 +68868,7 @@
         <v>44740</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>45722</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69014,7 +69014,7 @@
         <v>45174</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69092,7 +69092,7 @@
         <v>44818</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69165,7 +69165,7 @@
         <v>44917</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69238,7 +69238,7 @@
         <v>45530</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69316,7 +69316,7 @@
         <v>45544</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69389,7 +69389,7 @@
         <v>45646</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69462,7 +69462,7 @@
         <v>45744</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69540,7 +69540,7 @@
         <v>45037</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69618,7 +69618,7 @@
         <v>45037</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69691,7 +69691,7 @@
         <v>45505</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>45698</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69837,7 +69837,7 @@
         <v>45670</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69910,7 +69910,7 @@
         <v>45022</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69988,7 +69988,7 @@
         <v>44840</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70066,7 +70066,7 @@
         <v>45720</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>45111</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70212,7 +70212,7 @@
         <v>45775</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70285,7 +70285,7 @@
         <v>45714</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70363,7 +70363,7 @@
         <v>45761</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70436,7 +70436,7 @@
         <v>45065</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70509,7 +70509,7 @@
         <v>45572</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70582,7 +70582,7 @@
         <v>45210</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70660,7 +70660,7 @@
         <v>44914</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70738,7 +70738,7 @@
         <v>45755</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70811,7 +70811,7 @@
         <v>45469</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70884,7 +70884,7 @@
         <v>45082</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>44908</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71030,7 +71030,7 @@
         <v>45055</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71103,7 +71103,7 @@
         <v>45298</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71176,7 +71176,7 @@
         <v>44825</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71249,7 +71249,7 @@
         <v>45376</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71322,7 +71322,7 @@
         <v>45525</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71400,7 +71400,7 @@
         <v>44873</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71473,7 +71473,7 @@
         <v>45103</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71546,7 +71546,7 @@
         <v>45089</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71619,7 +71619,7 @@
         <v>45106</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71692,7 +71692,7 @@
         <v>45112</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71765,7 +71765,7 @@
         <v>44847</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71838,7 +71838,7 @@
         <v>45385</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71911,7 +71911,7 @@
         <v>45371</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71989,7 +71989,7 @@
         <v>45113</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72062,7 +72062,7 @@
         <v>45392</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72135,7 +72135,7 @@
         <v>44931</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72208,7 +72208,7 @@
         <v>45455</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72281,7 +72281,7 @@
         <v>44515</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72354,7 +72354,7 @@
         <v>44914</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72427,7 +72427,7 @@
         <v>45531</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72500,7 +72500,7 @@
         <v>45579</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72573,7 +72573,7 @@
         <v>45616</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72646,7 +72646,7 @@
         <v>45012</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72719,7 +72719,7 @@
         <v>45771</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72792,7 +72792,7 @@
         <v>45692</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72865,7 +72865,7 @@
         <v>44984</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72938,7 +72938,7 @@
         <v>45755</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73011,7 +73011,7 @@
         <v>45037</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73089,7 +73089,7 @@
         <v>45426</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73162,7 +73162,7 @@
         <v>45623</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73235,7 +73235,7 @@
         <v>45142</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73308,7 +73308,7 @@
         <v>45478</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73381,7 +73381,7 @@
         <v>45572</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73454,7 +73454,7 @@
         <v>45040</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73532,7 +73532,7 @@
         <v>44511</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73605,7 +73605,7 @@
         <v>45616</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73678,7 +73678,7 @@
         <v>45104</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73751,7 +73751,7 @@
         <v>45590</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73829,7 +73829,7 @@
         <v>45670</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73902,7 +73902,7 @@
         <v>45250</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73975,7 +73975,7 @@
         <v>45761</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74053,7 +74053,7 @@
         <v>44594</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74126,7 +74126,7 @@
         <v>44628</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74199,7 +74199,7 @@
         <v>45642</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74272,7 +74272,7 @@
         <v>45028</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74350,7 +74350,7 @@
         <v>45199</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74423,7 +74423,7 @@
         <v>45068</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74496,7 +74496,7 @@
         <v>45309</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74569,7 +74569,7 @@
         <v>44550</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74642,7 +74642,7 @@
         <v>45048</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74715,7 +74715,7 @@
         <v>45646</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74788,7 +74788,7 @@
         <v>45356</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74861,7 +74861,7 @@
         <v>45677</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74934,7 +74934,7 @@
         <v>45569</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75012,7 +75012,7 @@
         <v>45512</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75085,7 +75085,7 @@
         <v>45091</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75158,7 +75158,7 @@
         <v>45735</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75231,7 +75231,7 @@
         <v>45735</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75304,7 +75304,7 @@
         <v>45194</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75382,7 +75382,7 @@
         <v>45691</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75455,7 +75455,7 @@
         <v>45407</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75528,7 +75528,7 @@
         <v>45166</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75601,7 +75601,7 @@
         <v>45708</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75679,7 +75679,7 @@
         <v>45709</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75752,7 +75752,7 @@
         <v>45709</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75825,7 +75825,7 @@
         <v>45711</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75898,7 +75898,7 @@
         <v>45392</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75971,7 +75971,7 @@
         <v>45099</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76049,7 +76049,7 @@
         <v>44606</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76122,7 +76122,7 @@
         <v>45197</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76200,7 +76200,7 @@
         <v>45687</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76278,7 +76278,7 @@
         <v>45441</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76351,7 +76351,7 @@
         <v>45681</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76424,7 +76424,7 @@
         <v>44619</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76497,7 +76497,7 @@
         <v>45167</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76575,7 +76575,7 @@
         <v>44839</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76648,7 +76648,7 @@
         <v>45230</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76721,7 +76721,7 @@
         <v>45706</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76794,7 +76794,7 @@
         <v>45741</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76867,7 +76867,7 @@
         <v>45198</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76940,7 +76940,7 @@
         <v>44672</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77013,7 +77013,7 @@
         <v>45252</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77086,7 +77086,7 @@
         <v>45180</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77159,7 +77159,7 @@
         <v>45168</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77232,7 +77232,7 @@
         <v>44749</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77305,7 +77305,7 @@
         <v>45225</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77378,7 +77378,7 @@
         <v>45469</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77451,7 +77451,7 @@
         <v>45462</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         <v>45720</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -77597,7 +77597,7 @@
         <v>45215</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -77670,7 +77670,7 @@
         <v>45189</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -77748,7 +77748,7 @@
         <v>45217</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -77826,7 +77826,7 @@
         <v>45217</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -77904,7 +77904,7 @@
         <v>44805</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -77982,7 +77982,7 @@
         <v>44742</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78055,7 +78055,7 @@
         <v>44503</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78128,7 +78128,7 @@
         <v>45317</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78201,7 +78201,7 @@
         <v>45740</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78274,7 +78274,7 @@
         <v>44820</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78347,7 +78347,7 @@
         <v>45345</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78420,7 +78420,7 @@
         <v>45173</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78493,7 +78493,7 @@
         <v>45167</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -78566,7 +78566,7 @@
         <v>45216</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -78644,7 +78644,7 @@
         <v>45741</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -78717,7 +78717,7 @@
         <v>45205</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -78790,7 +78790,7 @@
         <v>45470</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -78863,7 +78863,7 @@
         <v>44900</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -78936,7 +78936,7 @@
         <v>45362</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>44606</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79082,7 +79082,7 @@
         <v>45226</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79160,7 +79160,7 @@
         <v>44949</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79233,7 +79233,7 @@
         <v>45561</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79306,7 +79306,7 @@
         <v>44610</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79379,7 +79379,7 @@
         <v>44726</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79452,7 +79452,7 @@
         <v>45713</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -79525,7 +79525,7 @@
         <v>45713</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -79598,7 +79598,7 @@
         <v>46108</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -79671,7 +79671,7 @@
         <v>46148</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>46286</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>46038</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45579</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>45342</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45546</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45562</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>45799</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45884</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45607</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45579</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45908</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>44772</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44826</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>44868</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44559</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45569</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>46282</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46286</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45523</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44715</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45723</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44925</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44645</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>46182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45562</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45581</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45264</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>46070</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45676</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46085</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45470</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>46275</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45019</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45938</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45952</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>46282</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>46104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>45873</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45562</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45695</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45831</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>46272</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45993</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45965</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45250</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45434</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45940</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44859</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44566</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45834</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45912</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>45019</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>46204</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45635</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>46055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>46093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45847</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46027</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>46027</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44619</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46269</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45567</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>46274</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>46155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45579</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44543</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45684</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45607</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45762</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44715</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44944</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45098</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45147</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45939</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46182</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>46202</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45120</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45426</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45624</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45749</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46283</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45488</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46287</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46052</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45558</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>46078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>46104</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>46308</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46308</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>46262</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46309</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44631</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46269</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>46314</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>46314</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45470</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46314</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>46272</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44644</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44631</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45840</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46275</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45086</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>46150</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46150</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>45569</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44837</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45099</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45481</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45110</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45043</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44772</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45275</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45576</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46135</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44824</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44587</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44784</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44652</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44777</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44846</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44606</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44854</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44687</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44524</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44742</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44841</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44813</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44846</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44859</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44599</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44872</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44802</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44609</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44851</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44846</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44619</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>44599</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>44830</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44588</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>44839</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44840</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44741</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44606</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44714</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>44846</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44606</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44838</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44606</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>44631</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44533</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44581</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45714</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45636</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44679</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45838</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45405</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>44825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44846</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45897</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45771</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45898</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45561</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45901</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45901</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>44620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45803</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45904</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45904</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45904</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44839</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45904</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>46160</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45898</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46161</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>46161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45909</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46162</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46161</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46161</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>46161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45912</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>46048</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45912</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45912</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44944</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44944</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>46010</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45916</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>46164</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44652</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>45915</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45918</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45917</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45552</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46168</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44944</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45919</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46167</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45922</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45923</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46030</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45154</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45923</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45925</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45926</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45926</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46167</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>44790</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46167</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45120</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45488</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45309</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>44980</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44841</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46169</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45930</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45418</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45929</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45091</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45091</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45932</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46171</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45208</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45933</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45597</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45938</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45247</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45940</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45939</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45030</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45944</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45944</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45427</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45943</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44846</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45078</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45698</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46008</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45832</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45016</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46177</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45448</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45635</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>44840</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45252</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45946</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45401</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45301</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45692</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46177</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46178</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46178</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45950</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45033</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45078</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45952</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>45951</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45951</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45951</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45249</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45952</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45952</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45952</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46182</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45952</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45952</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>46182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45953</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45953</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>46182</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45953</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45953</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>46183</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45714</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46183</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45252</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45957</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45957</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>46187</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45957</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>46185</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45957</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45630</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44606</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46185</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45959</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>44987</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>45070</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45615</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>46188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45940</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>46188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>46191</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45261</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45183</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45702</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>46195</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>46195</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45972</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46195</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45470</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>44592</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45043</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45975</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45975</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45604</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44802</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46198</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45222</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45975</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>45301</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>46198</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46198</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45980</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45273</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45982</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45981</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45463</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>46205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45756</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45681</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45982</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45706</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46205</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45737</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>45986</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46205</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46205</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45985</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46206</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45501</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45586</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45988</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45722</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>46211</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>46211</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45989</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45992</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46211</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45992</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>46213</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>46212</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46213</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45993</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>46212</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45749</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45037</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45604</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45630</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>45530</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45530</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45593</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45260</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45540</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45503</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45747</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>46000</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>46001</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45636</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46198</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>45777</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>46001</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>46006</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>46006</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>46195</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46006</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46006</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>46006</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45783</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>46008</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>46230</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45785</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>46233</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>46008</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46280</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46010</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46010</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45484</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46280</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>46013</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45785</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>46279</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>46280</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>46014</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>46239</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46020</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>46239</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45635</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>46239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45345</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>46281</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>46021</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46021</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46027</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46029</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45792</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46029</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46029</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46241</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45789</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45792</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>46240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>46034</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45455</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45792</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>46031</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>46286</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45572</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45140</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>46038</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45573</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>46287</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>46041</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45632</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>46041</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>46044</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46044</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>46044</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45243</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>46043</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>46287</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>46044</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>46287</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>46287</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>46287</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46244</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>46244</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>46244</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>46048</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>46245</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>46245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>46286</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>46287</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>46050</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>46050</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>46049</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>46050</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>46050</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>46049</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>46049</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>46246</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>46052</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>46289</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>46290</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>46247</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>46246</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45666</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>46247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>46058</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45447</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46289</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46059</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46059</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45237</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>46183</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>46059</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45524</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45811</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45623</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46248</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>46064</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>46293</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>46064</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>46063</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>46293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>46294</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>46064</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>46064</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46294</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46294</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45769</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>46066</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45439</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>46294</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>46294</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>46069</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>46071</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45471</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>46251</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45785</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45446</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>46071</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45824</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45824</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46073</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45824</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46073</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45559</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>46251</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>46251</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>46252</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45825</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>46078</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45825</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45825</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>46252</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>46252</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>46295</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>46252</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>46295</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>44873</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45832</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>46255</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45940</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45833</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>46087</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>46297</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>46246</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>46091</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45838</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46091</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>46254</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>46254</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53361,7 +53361,7 @@
         <v>46161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>46297</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>46093</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>44606</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45840</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46300</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53809,7 +53809,7 @@
         <v>45484</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         <v>46252</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45826</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>46297</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54101,7 +54101,7 @@
         <v>45842</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>46254</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45846</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>46100</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>46100</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54466,7 +54466,7 @@
         <v>46099</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45478</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>46245</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45481</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46105</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46105</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54904,7 +54904,7 @@
         <v>46301</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54977,7 +54977,7 @@
         <v>46259</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>46259</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>44874</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55206,7 +55206,7 @@
         <v>46259</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>46105</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46105</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55425,7 +55425,7 @@
         <v>46105</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55498,7 +55498,7 @@
         <v>46107</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
         <v>46259</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>46107</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>46301</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>46301</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>46259</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>46302</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>46259</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>45531</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>45531</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>46301</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>45803</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>46259</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>46113</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56550,7 +56550,7 @@
         <v>46259</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>46304</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>45866</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45428</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45470</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         <v>46303</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>45868</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>46119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45471</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>46120</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45033</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>46260</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46303</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45873</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46304</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>45874</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>46122</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>46304</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46122</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>45873</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>46260</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58113,7 +58113,7 @@
         <v>46304</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45876</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>45875</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58337,7 +58337,7 @@
         <v>46126</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>45875</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>45876</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46262</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>46308</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45877</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>46265</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58853,7 +58853,7 @@
         <v>46262</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>46262</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>46262</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>45681</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59160,7 +59160,7 @@
         <v>45545</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>45881</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45484</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59379,7 +59379,7 @@
         <v>45993</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59452,7 +59452,7 @@
         <v>45539</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>44939</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>45883</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46307</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>44902</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>45405</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59895,7 +59895,7 @@
         <v>46310</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>46309</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>46309</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>45938</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>46309</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60265,7 +60265,7 @@
         <v>44944</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>46310</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>45524</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60484,7 +60484,7 @@
         <v>46310</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45749</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>45722</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         <v>45561</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>44574</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60849,7 +60849,7 @@
         <v>45884</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45009</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60995,7 +60995,7 @@
         <v>45737</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61068,7 +61068,7 @@
         <v>45937</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61141,7 +61141,7 @@
         <v>45019</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>46314</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45905</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>45120</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45447</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>46268</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>46269</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61672,7 +61672,7 @@
         <v>46314</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61745,7 +61745,7 @@
         <v>46140</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>45581</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61891,7 +61891,7 @@
         <v>46262</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61969,7 +61969,7 @@
         <v>45572</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62042,7 +62042,7 @@
         <v>46269</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>46269</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62188,7 +62188,7 @@
         <v>46268</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62266,7 +62266,7 @@
         <v>46269</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62344,7 +62344,7 @@
         <v>46268</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45505</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45567</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>46316</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>46273</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62709,7 +62709,7 @@
         <v>46272</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62782,7 +62782,7 @@
         <v>45636</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62855,7 +62855,7 @@
         <v>45316</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62928,7 +62928,7 @@
         <v>45747</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63001,7 +63001,7 @@
         <v>46315</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>46041</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63147,7 +63147,7 @@
         <v>45827</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>46315</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63293,7 +63293,7 @@
         <v>45835</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63371,7 +63371,7 @@
         <v>46316</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>46272</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45908</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>45047</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>46272</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63736,7 +63736,7 @@
         <v>45576</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63814,7 +63814,7 @@
         <v>46070</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>44629</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>44606</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64033,7 +64033,7 @@
         <v>46140</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64111,7 +64111,7 @@
         <v>45923</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>45722</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>46274</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64335,7 +64335,7 @@
         <v>46318</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64413,7 +64413,7 @@
         <v>46318</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>46318</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>46141</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64642,7 +64642,7 @@
         <v>46276</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45432</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64793,7 +64793,7 @@
         <v>46276</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64871,7 +64871,7 @@
         <v>45965</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64944,7 +64944,7 @@
         <v>46141</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>44937</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65090,7 +65090,7 @@
         <v>46276</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65163,7 +65163,7 @@
         <v>45812</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65236,7 +65236,7 @@
         <v>46276</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65309,7 +65309,7 @@
         <v>46141</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>45702</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>46141</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>45923</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>46141</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>44983</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>45244</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65825,7 +65825,7 @@
         <v>46146</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65898,7 +65898,7 @@
         <v>45747</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65971,7 +65971,7 @@
         <v>46274</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>45756</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>46146</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66200,7 +66200,7 @@
         <v>46281</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66273,7 +66273,7 @@
         <v>46287</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66346,7 +66346,7 @@
         <v>45790</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66419,7 +66419,7 @@
         <v>45399</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66492,7 +66492,7 @@
         <v>46148</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>45211</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>46150</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66721,7 +66721,7 @@
         <v>46153</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66794,7 +66794,7 @@
         <v>46154</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66867,7 +66867,7 @@
         <v>46154</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66940,7 +66940,7 @@
         <v>45594</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67013,7 +67013,7 @@
         <v>46155</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67086,7 +67086,7 @@
         <v>45271</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67159,7 +67159,7 @@
         <v>45629</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67232,7 +67232,7 @@
         <v>44920</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67305,7 +67305,7 @@
         <v>45965</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67378,7 +67378,7 @@
         <v>46156</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45348</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67529,7 +67529,7 @@
         <v>45013</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>46160</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67680,7 +67680,7 @@
         <v>45343</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67753,7 +67753,7 @@
         <v>45244</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67826,7 +67826,7 @@
         <v>45580</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67899,7 +67899,7 @@
         <v>45007</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45623</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         <v>45641</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68123,7 +68123,7 @@
         <v>45041</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68201,7 +68201,7 @@
         <v>45041</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68279,7 +68279,7 @@
         <v>45706</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68352,7 +68352,7 @@
         <v>45639</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68425,7 +68425,7 @@
         <v>44805</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68503,7 +68503,7 @@
         <v>45041</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68576,7 +68576,7 @@
         <v>44715</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68649,7 +68649,7 @@
         <v>45427</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68722,7 +68722,7 @@
         <v>44900</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68795,7 +68795,7 @@
         <v>44774</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68868,7 +68868,7 @@
         <v>44740</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>45722</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69014,7 +69014,7 @@
         <v>45174</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69092,7 +69092,7 @@
         <v>44818</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69165,7 +69165,7 @@
         <v>44917</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69238,7 +69238,7 @@
         <v>45530</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69316,7 +69316,7 @@
         <v>45544</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69389,7 +69389,7 @@
         <v>45646</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69462,7 +69462,7 @@
         <v>45744</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69540,7 +69540,7 @@
         <v>45037</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69618,7 +69618,7 @@
         <v>45037</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69691,7 +69691,7 @@
         <v>45505</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>45698</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69837,7 +69837,7 @@
         <v>45670</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69910,7 +69910,7 @@
         <v>45022</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69988,7 +69988,7 @@
         <v>44840</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70066,7 +70066,7 @@
         <v>45720</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70139,7 +70139,7 @@
         <v>45111</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70212,7 +70212,7 @@
         <v>45775</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70285,7 +70285,7 @@
         <v>45714</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70363,7 +70363,7 @@
         <v>45761</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70436,7 +70436,7 @@
         <v>45065</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70509,7 +70509,7 @@
         <v>45572</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70582,7 +70582,7 @@
         <v>45210</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70660,7 +70660,7 @@
         <v>44914</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70738,7 +70738,7 @@
         <v>45755</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70811,7 +70811,7 @@
         <v>45469</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70884,7 +70884,7 @@
         <v>45082</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>44908</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71030,7 +71030,7 @@
         <v>45055</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71103,7 +71103,7 @@
         <v>45298</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71176,7 +71176,7 @@
         <v>44825</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71249,7 +71249,7 @@
         <v>45376</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71322,7 +71322,7 @@
         <v>45525</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71400,7 +71400,7 @@
         <v>44873</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71473,7 +71473,7 @@
         <v>45103</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71546,7 +71546,7 @@
         <v>45089</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71619,7 +71619,7 @@
         <v>45106</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71692,7 +71692,7 @@
         <v>45112</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71765,7 +71765,7 @@
         <v>44847</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71838,7 +71838,7 @@
         <v>45385</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -71911,7 +71911,7 @@
         <v>45371</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71989,7 +71989,7 @@
         <v>45113</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72062,7 +72062,7 @@
         <v>45392</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72135,7 +72135,7 @@
         <v>44931</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72208,7 +72208,7 @@
         <v>45455</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72281,7 +72281,7 @@
         <v>44515</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72354,7 +72354,7 @@
         <v>44914</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72427,7 +72427,7 @@
         <v>45531</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72500,7 +72500,7 @@
         <v>45579</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72573,7 +72573,7 @@
         <v>45616</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72646,7 +72646,7 @@
         <v>45012</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72719,7 +72719,7 @@
         <v>45771</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72792,7 +72792,7 @@
         <v>45692</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -72865,7 +72865,7 @@
         <v>44984</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72938,7 +72938,7 @@
         <v>45755</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73011,7 +73011,7 @@
         <v>45037</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73089,7 +73089,7 @@
         <v>45426</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73162,7 +73162,7 @@
         <v>45623</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73235,7 +73235,7 @@
         <v>45142</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73308,7 +73308,7 @@
         <v>45478</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73381,7 +73381,7 @@
         <v>45572</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73454,7 +73454,7 @@
         <v>45040</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73532,7 +73532,7 @@
         <v>44511</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73605,7 +73605,7 @@
         <v>45616</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73678,7 +73678,7 @@
         <v>45104</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73751,7 +73751,7 @@
         <v>45590</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -73829,7 +73829,7 @@
         <v>45670</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73902,7 +73902,7 @@
         <v>45250</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73975,7 +73975,7 @@
         <v>45761</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74053,7 +74053,7 @@
         <v>44594</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74126,7 +74126,7 @@
         <v>44628</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74199,7 +74199,7 @@
         <v>45642</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74272,7 +74272,7 @@
         <v>45028</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74350,7 +74350,7 @@
         <v>45199</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74423,7 +74423,7 @@
         <v>45068</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74496,7 +74496,7 @@
         <v>45309</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74569,7 +74569,7 @@
         <v>44550</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74642,7 +74642,7 @@
         <v>45048</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74715,7 +74715,7 @@
         <v>45646</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -74788,7 +74788,7 @@
         <v>45356</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -74861,7 +74861,7 @@
         <v>45677</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74934,7 +74934,7 @@
         <v>45569</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75012,7 +75012,7 @@
         <v>45512</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75085,7 +75085,7 @@
         <v>45091</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75158,7 +75158,7 @@
         <v>45735</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75231,7 +75231,7 @@
         <v>45735</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75304,7 +75304,7 @@
         <v>45194</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75382,7 +75382,7 @@
         <v>45691</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75455,7 +75455,7 @@
         <v>45407</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75528,7 +75528,7 @@
         <v>45166</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75601,7 +75601,7 @@
         <v>45708</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75679,7 +75679,7 @@
         <v>45709</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -75752,7 +75752,7 @@
         <v>45709</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -75825,7 +75825,7 @@
         <v>45711</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -75898,7 +75898,7 @@
         <v>45392</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -75971,7 +75971,7 @@
         <v>45099</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76049,7 +76049,7 @@
         <v>44606</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76122,7 +76122,7 @@
         <v>45197</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76200,7 +76200,7 @@
         <v>45687</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76278,7 +76278,7 @@
         <v>45441</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76351,7 +76351,7 @@
         <v>45681</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76424,7 +76424,7 @@
         <v>44619</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76497,7 +76497,7 @@
         <v>45167</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76575,7 +76575,7 @@
         <v>44839</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -76648,7 +76648,7 @@
         <v>45230</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -76721,7 +76721,7 @@
         <v>45706</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -76794,7 +76794,7 @@
         <v>45741</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -76867,7 +76867,7 @@
         <v>45198</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -76940,7 +76940,7 @@
         <v>44672</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77013,7 +77013,7 @@
         <v>45252</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77086,7 +77086,7 @@
         <v>45180</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77159,7 +77159,7 @@
         <v>45168</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77232,7 +77232,7 @@
         <v>44749</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77305,7 +77305,7 @@
         <v>45225</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77378,7 +77378,7 @@
         <v>45469</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77451,7 +77451,7 @@
         <v>45462</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         <v>45720</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -77597,7 +77597,7 @@
         <v>45215</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -77670,7 +77670,7 @@
         <v>45189</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -77748,7 +77748,7 @@
         <v>45217</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -77826,7 +77826,7 @@
         <v>45217</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -77904,7 +77904,7 @@
         <v>44805</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -77982,7 +77982,7 @@
         <v>44742</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78055,7 +78055,7 @@
         <v>44503</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78128,7 +78128,7 @@
         <v>45317</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78201,7 +78201,7 @@
         <v>45740</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78274,7 +78274,7 @@
         <v>44820</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78347,7 +78347,7 @@
         <v>45345</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78420,7 +78420,7 @@
         <v>45173</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78493,7 +78493,7 @@
         <v>45167</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -78566,7 +78566,7 @@
         <v>45216</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -78644,7 +78644,7 @@
         <v>45741</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -78717,7 +78717,7 @@
         <v>45205</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -78790,7 +78790,7 @@
         <v>45470</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -78863,7 +78863,7 @@
         <v>44900</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -78936,7 +78936,7 @@
         <v>45362</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>44606</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79082,7 +79082,7 @@
         <v>45226</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79160,7 +79160,7 @@
         <v>44949</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79233,7 +79233,7 @@
         <v>45561</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79306,7 +79306,7 @@
         <v>44610</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79379,7 +79379,7 @@
         <v>44726</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79452,7 +79452,7 @@
         <v>45713</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -79525,7 +79525,7 @@
         <v>45713</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -79598,7 +79598,7 @@
         <v>46108</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -79671,7 +79671,7 @@
         <v>46148</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>46286</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
